--- a/s2022_random10_lambda_residuals.xlsx
+++ b/s2022_random10_lambda_residuals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitra\Downloads\matlab analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0377A6B-09F7-44D9-AF2F-7B910E06D492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ACAC5D-AA62-4F27-BDD7-18814188BBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2408,25 +2408,25 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="B2">
-        <v>88.178083078669459</v>
+        <v>88.731296113110744</v>
       </c>
       <c r="C2">
-        <v>19.125686708098325</v>
+        <v>19.117137026610163</v>
       </c>
       <c r="D2">
-        <v>21904690.71195899</v>
+        <v>1039732.9005497133</v>
       </c>
       <c r="E2">
-        <v>63082.050421550484</v>
+        <v>56144.064423947595</v>
       </c>
       <c r="F2">
-        <v>11543842.114061868</v>
+        <v>279490.13886148616</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2.0285975378323644</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -2437,25 +2437,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="B3">
-        <v>88.179712089061042</v>
+        <v>89.041259229576752</v>
       </c>
       <c r="C3">
-        <v>19.122617492643222</v>
+        <v>19.1154412402256</v>
       </c>
       <c r="D3">
-        <v>16460403.13917641</v>
+        <v>643369.8384231762</v>
       </c>
       <c r="E3">
-        <v>61702.249595430621</v>
+        <v>55727.244904376879</v>
       </c>
       <c r="F3">
-        <v>8530121.5591043532</v>
+        <v>116718.5258003206</v>
       </c>
       <c r="G3">
-        <v>2.3286560563844176</v>
+        <v>1.0531892606649045</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2466,25 +2466,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="B4">
-        <v>88.187920447538986</v>
+        <v>89.536424645485411</v>
       </c>
       <c r="C4">
-        <v>19.11420334101329</v>
+        <v>19.061027624833983</v>
       </c>
       <c r="D4">
-        <v>10824377.625586743</v>
+        <v>389290.78288972174</v>
       </c>
       <c r="E4">
-        <v>60277.845335265949</v>
+        <v>55363.063697549398</v>
       </c>
       <c r="F4">
-        <v>7445835.4032958401</v>
+        <v>85769.17625665087</v>
       </c>
       <c r="G4">
-        <v>1.8105190156411528</v>
+        <v>0.68912204095210616</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2495,25 +2495,25 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="B5">
-        <v>88.214088172360334</v>
+        <v>90.324508020781821</v>
       </c>
       <c r="C5">
-        <v>19.101642403279016</v>
+        <v>18.973047953767527</v>
       </c>
       <c r="D5">
-        <v>6591561.2183982898</v>
+        <v>227267.16860329913</v>
       </c>
       <c r="E5">
-        <v>58995.952999510555</v>
+        <v>55037.599635848674</v>
       </c>
       <c r="F5">
-        <v>3984178.9373016893</v>
+        <v>40275.131831384788</v>
       </c>
       <c r="G5">
-        <v>1.1672031302252202</v>
+        <v>0.36304260987478831</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2524,25 +2524,25 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="B6">
-        <v>88.285771768440952</v>
+        <v>91.434126022902134</v>
       </c>
       <c r="C6">
-        <v>19.088476097584604</v>
+        <v>18.872907267651406</v>
       </c>
       <c r="D6">
-        <v>3945533.0737594566</v>
+        <v>131186.00252626222</v>
       </c>
       <c r="E6">
-        <v>57898.102211743499</v>
+        <v>54752.223219536747</v>
       </c>
       <c r="F6">
-        <v>1731338.6543124821</v>
+        <v>15572.531713437862</v>
       </c>
       <c r="G6">
-        <v>0.72270257899608581</v>
+        <v>0.1761965211053349</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2553,25 +2553,25 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="B7">
-        <v>88.4379412189965</v>
+        <v>93.00768549187481</v>
       </c>
       <c r="C7">
-        <v>19.090337790370999</v>
+        <v>18.826050141991605</v>
       </c>
       <c r="D7">
-        <v>2156744.824430787</v>
+        <v>78803.835072276634</v>
       </c>
       <c r="E7">
-        <v>56961.970468217776</v>
+        <v>54524.173534324582</v>
       </c>
       <c r="F7">
-        <v>730642.26094206516</v>
+        <v>9383.3431392203365</v>
       </c>
       <c r="G7">
-        <v>0.44480061635755086</v>
+        <v>9.9124087364528241E-2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2582,25 +2582,25 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="B8">
-        <v>88.731296113110744</v>
+        <v>95.563087654116046</v>
       </c>
       <c r="C8">
-        <v>19.117137026610163</v>
+        <v>19.012955740612739</v>
       </c>
       <c r="D8">
-        <v>1039732.9005497133</v>
+        <v>49714.246393557813</v>
       </c>
       <c r="E8">
-        <v>56144.064423947595</v>
+        <v>54628.588740746163</v>
       </c>
       <c r="F8">
-        <v>224832.46723139234</v>
+        <v>4129.7120810012011</v>
       </c>
       <c r="G8">
-        <v>0.25431661042770132</v>
+        <v>5.3894867860018861E-2</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2611,54 +2611,54 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="B9">
-        <v>89.345345861624779</v>
+        <v>100.38299671818847</v>
       </c>
       <c r="C9">
-        <v>19.083102229341172</v>
+        <v>19.82975525041142</v>
       </c>
       <c r="D9">
-        <v>461941.21094709996</v>
+        <v>32743.57168165566</v>
       </c>
       <c r="E9">
-        <v>55480.422441490591</v>
+        <v>55891.340102941635</v>
       </c>
       <c r="F9">
-        <v>99000.686589312027</v>
+        <v>2378.3478422471171</v>
       </c>
       <c r="G9">
-        <v>0.13944289061245052</v>
+        <v>5.3431186333139792E-2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="B10">
-        <v>90.649276603547051</v>
+        <v>109.57419755109781</v>
       </c>
       <c r="C10">
-        <v>18.943228310778991</v>
+        <v>22.182969536364734</v>
       </c>
       <c r="D10">
-        <v>188026.37171718688</v>
+        <v>21306.838469288072</v>
       </c>
       <c r="E10">
-        <v>54938.662893532004</v>
+        <v>60281.323560912919</v>
       </c>
       <c r="F10">
-        <v>25660.111910496107</v>
+        <v>1116.511244436279</v>
       </c>
       <c r="G10">
-        <v>5.7256196824631796E-2</v>
+        <v>0.11530397870621745</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2669,54 +2669,54 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="B11">
-        <v>93.00768549187481</v>
+        <v>124.58723832827522</v>
       </c>
       <c r="C11">
-        <v>18.826050141991605</v>
+        <v>27.201566491543886</v>
       </c>
       <c r="D11">
-        <v>78803.835072276634</v>
+        <v>13638.967091905322</v>
       </c>
       <c r="E11">
-        <v>54524.173534324582</v>
+        <v>72887.687952057298</v>
       </c>
       <c r="F11">
-        <v>8649.9732996772473</v>
+        <v>698.69372176785225</v>
       </c>
       <c r="G11">
-        <v>2.353770068525639E-3</v>
+        <v>0.32891260752596463</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="B12">
-        <v>98.406539719587229</v>
+        <v>146.01485898128578</v>
       </c>
       <c r="C12">
-        <v>19.431628389838384</v>
+        <v>35.512703730271937</v>
       </c>
       <c r="D12">
-        <v>37513.289012641639</v>
+        <v>10111.770069099503</v>
       </c>
       <c r="E12">
-        <v>55247.547534378406</v>
+        <v>111168.59163488385</v>
       </c>
       <c r="F12">
-        <v>3277.5288174546358</v>
+        <v>336.46911539592463</v>
       </c>
       <c r="G12">
-        <v>8.4527273479895859E-2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D2">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2801,22 +2801,22 @@
         <v>9.5299999999999994</v>
       </c>
       <c r="B2">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-4</v>
       </c>
       <c r="C2">
-        <v>102.57873060086148</v>
+        <v>104.02014287426198</v>
       </c>
       <c r="D2">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E2">
-        <v>64540.369271911703</v>
+        <v>26503.750759525967</v>
       </c>
       <c r="F2">
-        <v>62471.591803261304</v>
+        <v>65480.25523688738</v>
       </c>
       <c r="G2">
-        <v>27602.04877831116</v>
+        <v>7783.2335002287455</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2824,22 +2824,22 @@
         <v>14.53</v>
       </c>
       <c r="B3">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C3">
-        <v>92.239115088018053</v>
+        <v>93.516472903435599</v>
       </c>
       <c r="D3">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E3">
-        <v>40881.108326016612</v>
+        <v>15205.998595947409</v>
       </c>
       <c r="F3">
-        <v>51424.189332379203</v>
+        <v>54736.643257747535</v>
       </c>
       <c r="G3">
-        <v>16462.20976513379</v>
+        <v>6778.7128503917293</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2847,22 +2847,22 @@
         <v>59.55</v>
       </c>
       <c r="B4">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C4">
-        <v>75.864207869188405</v>
+        <v>76.801713118660189</v>
       </c>
       <c r="D4">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E4">
-        <v>49137.393162051376</v>
+        <v>23118.794842413834</v>
       </c>
       <c r="F4">
-        <v>48747.631914431608</v>
+        <v>50444.508333366437</v>
       </c>
       <c r="G4">
-        <v>5520.806346299637</v>
+        <v>1568.7025697136655</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2870,22 +2870,22 @@
         <v>84.52</v>
       </c>
       <c r="B5">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C5">
-        <v>73.201761670720444</v>
+        <v>73.686195856618639</v>
       </c>
       <c r="D5">
-        <v>3.1622776601683794E-3</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="E5">
-        <v>50356.633379202118</v>
+        <v>32388.849713649612</v>
       </c>
       <c r="F5">
-        <v>48552.814308068038</v>
+        <v>48765.315887796343</v>
       </c>
       <c r="G5">
-        <v>5494.6043568566156</v>
+        <v>3387.4943086734811</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2893,22 +2893,22 @@
         <v>94.52</v>
       </c>
       <c r="B6">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C6">
-        <v>75.623544525989104</v>
+        <v>76.088814272539608</v>
       </c>
       <c r="D6">
-        <v>3.1622776601683794E-3</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="E6">
-        <v>48218.535681814858</v>
+        <v>32246.162737942508</v>
       </c>
       <c r="F6">
-        <v>50288.063506718005</v>
+        <v>50463.981831185221</v>
       </c>
       <c r="G6">
-        <v>8195.5869251459571</v>
+        <v>2760.3063433026841</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2916,22 +2916,22 @@
         <v>104.55</v>
       </c>
       <c r="B7">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C7">
-        <v>73.395324049711746</v>
+        <v>74.028814332326576</v>
       </c>
       <c r="D7">
-        <v>3.1622776601683794E-3</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="E7">
-        <v>49681.709289034792</v>
+        <v>32463.119649426484</v>
       </c>
       <c r="F7">
-        <v>49277.880212534372</v>
+        <v>49426.707550185332</v>
       </c>
       <c r="G7">
-        <v>11914.193464255941</v>
+        <v>2387.7138104851574</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>86.82995976033817</v>
       </c>
       <c r="D8">
-        <v>3.1622776601683794E-3</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="E8">
-        <v>107494.3236406161</v>
+        <v>65860.870928385557</v>
       </c>
       <c r="F8">
-        <v>53600.68386089147</v>
+        <v>53681.49179913634</v>
       </c>
       <c r="G8">
-        <v>3022.6766933995696</v>
+        <v>1417.1236611721922</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2962,22 +2962,22 @@
         <v>199.6</v>
       </c>
       <c r="B9">
-        <v>3.1622776601683792E-7</v>
+        <v>1E-4</v>
       </c>
       <c r="C9">
-        <v>107.21228033837279</v>
+        <v>107.27318768125413</v>
       </c>
       <c r="D9">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E9">
-        <v>79347.708423338598</v>
+        <v>40394.727884571206</v>
       </c>
       <c r="F9">
-        <v>60561.479134422865</v>
+        <v>61132.335585166882</v>
       </c>
       <c r="G9">
-        <v>5785.1256218543504</v>
+        <v>1088.3207566690742</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2985,22 +2985,22 @@
         <v>209.57</v>
       </c>
       <c r="B10">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C10">
-        <v>127.23981343720133</v>
+        <v>127.41263750937229</v>
       </c>
       <c r="D10">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E10">
-        <v>234877.07020140468</v>
+        <v>84471.05600454667</v>
       </c>
       <c r="F10">
-        <v>70474.670578018427</v>
+        <v>70598.030445816446</v>
       </c>
       <c r="G10">
-        <v>1158.0361372356781</v>
+        <v>544.54106140634269</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3008,22 +3008,22 @@
         <v>239.94</v>
       </c>
       <c r="B11">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="C11">
-        <v>67.550531046620833</v>
+        <v>67.655022822300225</v>
       </c>
       <c r="D11">
-        <v>3.1622776601683794E-3</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="E11">
-        <v>63503.499347375604</v>
+        <v>26882.671810963799</v>
       </c>
       <c r="F11">
-        <v>49842.730692520447</v>
+        <v>50166.831565601911</v>
       </c>
       <c r="G11">
-        <v>1344.444908279776</v>
+        <v>337.06988775001969</v>
       </c>
     </row>
   </sheetData>
@@ -3088,37 +3088,37 @@
         <v>198</v>
       </c>
       <c r="C2">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D2">
-        <v>74.858023672208859</v>
+        <v>74.761876495189327</v>
       </c>
       <c r="E2">
-        <v>102.6058734864463</v>
+        <v>104.02014287426198</v>
       </c>
       <c r="F2">
-        <v>221.11095768856791</v>
+        <v>221.36988815522582</v>
       </c>
       <c r="G2">
-        <v>45735805.901726864</v>
+        <v>497392.83148469887</v>
       </c>
       <c r="H2">
-        <v>7522.7127109994435</v>
+        <v>7232.2768934101096</v>
       </c>
       <c r="I2">
-        <v>111474.45545956769</v>
+        <v>63542.114885650699</v>
       </c>
       <c r="J2">
-        <v>118997.16817056714</v>
+        <v>70774.39177906081</v>
       </c>
       <c r="K2">
-        <v>40685831.133002743</v>
+        <v>1109354.8592855555</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2.0511252357801881</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -3132,34 +3132,34 @@
         <v>198</v>
       </c>
       <c r="C3">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D3">
-        <v>74.839638116172011</v>
+        <v>74.694235691779753</v>
       </c>
       <c r="E3">
-        <v>102.59612967134134</v>
+        <v>104.62002403292306</v>
       </c>
       <c r="F3">
-        <v>221.11304125973811</v>
+        <v>221.49957750876811</v>
       </c>
       <c r="G3">
-        <v>29401054.331855014</v>
+        <v>353236.50624859077</v>
       </c>
       <c r="H3">
-        <v>7524.1679840650659</v>
+        <v>7064.6693967555839</v>
       </c>
       <c r="I3">
-        <v>101391.47626724339</v>
+        <v>61307.842973252249</v>
       </c>
       <c r="J3">
-        <v>108915.64425130845</v>
+        <v>68372.51237000784</v>
       </c>
       <c r="K3">
-        <v>32180662.998124663</v>
+        <v>434718.87754569302</v>
       </c>
       <c r="L3">
-        <v>2.255142597850869</v>
+        <v>1.1329582328633572</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -3176,37 +3176,37 @@
         <v>198</v>
       </c>
       <c r="C4">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D4">
-        <v>74.717112814831864</v>
+        <v>74.270255120058167</v>
       </c>
       <c r="E4">
-        <v>102.57873060086148</v>
+        <v>105.36119026236544</v>
       </c>
       <c r="F4">
-        <v>221.11975990213429</v>
+        <v>221.69091805811328</v>
       </c>
       <c r="G4">
-        <v>15497294.087810714</v>
+        <v>234651.41850945787</v>
       </c>
       <c r="H4">
-        <v>7530.5012052456887</v>
+        <v>6890.1112172898747</v>
       </c>
       <c r="I4">
-        <v>91045.893396032916</v>
+        <v>59438.951748344705</v>
       </c>
       <c r="J4">
-        <v>98576.394601278604</v>
+        <v>66329.062965634585</v>
       </c>
       <c r="K4">
-        <v>26516788.232061315</v>
+        <v>368729.86998065066</v>
       </c>
       <c r="L4">
-        <v>1.628769170825755</v>
+        <v>0.81845059319048319</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3220,34 +3220,34 @@
         <v>198</v>
       </c>
       <c r="C5">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D5">
-        <v>74.58789674259927</v>
+        <v>73.505741993740187</v>
       </c>
       <c r="E5">
-        <v>102.60003086018001</v>
+        <v>106.50507089196572</v>
       </c>
       <c r="F5">
-        <v>221.13486541256285</v>
+        <v>221.99788808405935</v>
       </c>
       <c r="G5">
-        <v>6721304.4547582874</v>
+        <v>151900.70656067072</v>
       </c>
       <c r="H5">
-        <v>7557.8251783966698</v>
+        <v>6742.3553366577171</v>
       </c>
       <c r="I5">
-        <v>81974.578233050357</v>
+        <v>57890.962517365464</v>
       </c>
       <c r="J5">
-        <v>89532.403411447027</v>
+        <v>64633.317854023182</v>
       </c>
       <c r="K5">
-        <v>13275422.688317165</v>
+        <v>140940.49130548182</v>
       </c>
       <c r="L5">
-        <v>0.95121260424427123</v>
+        <v>0.43334508804950456</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3264,34 +3264,34 @@
         <v>198</v>
       </c>
       <c r="C6">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D6">
-        <v>74.486249906286687</v>
+        <v>72.578447523184522</v>
       </c>
       <c r="E6">
-        <v>102.77463481239108</v>
+        <v>108.2654416088905</v>
       </c>
       <c r="F6">
-        <v>221.16770956925259</v>
+        <v>222.49415114040181</v>
       </c>
       <c r="G6">
-        <v>2668419.3346865154</v>
+        <v>97482.421825096913</v>
       </c>
       <c r="H6">
-        <v>7553.7458044619571</v>
+        <v>6653.7515730567493</v>
       </c>
       <c r="I6">
-        <v>74375.519600881991</v>
+        <v>56777.816831547018</v>
       </c>
       <c r="J6">
-        <v>81929.265405343947</v>
+        <v>63431.568404603764</v>
       </c>
       <c r="K6">
-        <v>7443725.251271219</v>
+        <v>52868.325532440031</v>
       </c>
       <c r="L6">
-        <v>0.58465495532729927</v>
+        <v>0.23525847596290506</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3308,34 +3308,34 @@
         <v>198</v>
       </c>
       <c r="C7">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D7">
-        <v>74.578186661263956</v>
+        <v>71.360721523222338</v>
       </c>
       <c r="E7">
-        <v>103.23224955182428</v>
+        <v>111.15579010917465</v>
       </c>
       <c r="F7">
-        <v>221.23570417575652</v>
+        <v>223.34505909599804</v>
       </c>
       <c r="G7">
-        <v>1055967.7930880268</v>
+        <v>64540.369271911703</v>
       </c>
       <c r="H7">
-        <v>7447.7171372716821</v>
+        <v>6745.053657071031</v>
       </c>
       <c r="I7">
-        <v>68259.151259685605</v>
+        <v>55726.538146190273</v>
       </c>
       <c r="J7">
-        <v>75706.868396957288</v>
+        <v>62471.591803261304</v>
       </c>
       <c r="K7">
-        <v>2304462.6776403831</v>
+        <v>27422.604257845775</v>
       </c>
       <c r="L7">
-        <v>0.31294432231438768</v>
+        <v>0.13906968013161636</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -3352,34 +3352,34 @@
         <v>198</v>
       </c>
       <c r="C8">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D8">
-        <v>74.761876495189327</v>
+        <v>69.413213782791217</v>
       </c>
       <c r="E8">
-        <v>104.02014287426198</v>
+        <v>116.471221950158</v>
       </c>
       <c r="F8">
-        <v>221.36988815522582</v>
+        <v>224.98358285752607</v>
       </c>
       <c r="G8">
-        <v>497392.83148469887</v>
+        <v>42394.547425424164</v>
       </c>
       <c r="H8">
-        <v>7232.2768934101096</v>
+        <v>7457.0824495947145</v>
       </c>
       <c r="I8">
-        <v>63542.114885650699</v>
+        <v>54965.324890257558</v>
       </c>
       <c r="J8">
-        <v>70774.39177906081</v>
+        <v>62422.407339852274</v>
       </c>
       <c r="K8">
-        <v>621131.2414673625</v>
+        <v>12534.205516445765</v>
       </c>
       <c r="L8">
-        <v>0.1720769204234891</v>
+        <v>8.0055815382540071E-2</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -3396,40 +3396,40 @@
         <v>198</v>
       </c>
       <c r="C9">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D9">
-        <v>74.463857284298712</v>
+        <v>65.791571586607446</v>
       </c>
       <c r="E9">
-        <v>105.09570776674815</v>
+        <v>126.51076672142855</v>
       </c>
       <c r="F9">
-        <v>221.61971651942787</v>
+        <v>228.4112687423877</v>
       </c>
       <c r="G9">
-        <v>265651.58451293991</v>
+        <v>26503.750759525967</v>
       </c>
       <c r="H9">
-        <v>6944.9418168809334</v>
+        <v>10140.407716860735</v>
       </c>
       <c r="I9">
-        <v>60025.260245059399</v>
+        <v>55339.847520026648</v>
       </c>
       <c r="J9">
-        <v>66970.202061940334</v>
+        <v>65480.25523688738</v>
       </c>
       <c r="K9">
-        <v>456289.27291976486</v>
+        <v>7783.2335002287455</v>
       </c>
       <c r="L9">
-        <v>9.5653450543534344E-2</v>
+        <v>6.1997043826779258E-2</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3440,34 +3440,34 @@
         <v>198</v>
       </c>
       <c r="C10">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D10">
-        <v>73.219225474825308</v>
+        <v>59.909784531387835</v>
       </c>
       <c r="E10">
-        <v>107.0109903689915</v>
+        <v>144.14396806198835</v>
       </c>
       <c r="F10">
-        <v>222.13729519417075</v>
+        <v>235.56883492947989</v>
       </c>
       <c r="G10">
-        <v>129663.61360746319</v>
+        <v>14499.202169260505</v>
       </c>
       <c r="H10">
-        <v>6700.7582673217294</v>
+        <v>18876.875765811259</v>
       </c>
       <c r="I10">
-        <v>57509.953275316722</v>
+        <v>58115.627349918424</v>
       </c>
       <c r="J10">
-        <v>64210.711542638455</v>
+        <v>76992.503115729691</v>
       </c>
       <c r="K10">
-        <v>97782.576377319478</v>
+        <v>3612.2232558955707</v>
       </c>
       <c r="L10">
-        <v>3.504568290867232E-2</v>
+        <v>0.10415948445682592</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -3484,40 +3484,40 @@
         <v>198</v>
       </c>
       <c r="C11">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D11">
-        <v>71.360721523222338</v>
+        <v>52.494343412353778</v>
       </c>
       <c r="E11">
-        <v>111.15579010917465</v>
+        <v>171.77598908137904</v>
       </c>
       <c r="F11">
-        <v>223.34505909599804</v>
+        <v>250.26837234355477</v>
       </c>
       <c r="G11">
-        <v>64540.369271911703</v>
+        <v>8295.5710430782729</v>
       </c>
       <c r="H11">
-        <v>6745.053657071031</v>
+        <v>47511.873911428433</v>
       </c>
       <c r="I11">
-        <v>55726.538146190273</v>
+        <v>64519.447854688682</v>
       </c>
       <c r="J11">
-        <v>62471.591803261304</v>
+        <v>112031.32176611712</v>
       </c>
       <c r="K11">
-        <v>27602.04877831116</v>
+        <v>2446.2825755705121</v>
       </c>
       <c r="L11">
-        <v>1.1284419297207132E-3</v>
+        <v>0.30490771547951978</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3528,34 +3528,34 @@
         <v>198</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
-        <v>67.214334061550332</v>
+        <v>45.695667087453408</v>
       </c>
       <c r="E12">
-        <v>122.41526250866939</v>
+        <v>211.99121275679792</v>
       </c>
       <c r="F12">
-        <v>226.97071482850967</v>
+        <v>279.19822565073787</v>
       </c>
       <c r="G12">
-        <v>31907.460720867995</v>
+        <v>8906.7634014103623</v>
       </c>
       <c r="H12">
-        <v>8870.4387558940343</v>
+        <v>147192.61007569186</v>
       </c>
       <c r="I12">
-        <v>54926.535143693232</v>
+        <v>78593.04267035659</v>
       </c>
       <c r="J12">
-        <v>63796.973899587269</v>
+        <v>225785.65274604846</v>
       </c>
       <c r="K12">
-        <v>10744.876836017216</v>
+        <v>1077.2482272469431</v>
       </c>
       <c r="L12">
-        <v>2.3447476018883369E-2</v>
+        <v>1.0012496335754983</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -3572,34 +3572,34 @@
         <v>198</v>
       </c>
       <c r="C13">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D13">
-        <v>77.333451750862565</v>
+        <v>77.136326010048407</v>
       </c>
       <c r="E13">
-        <v>92.239115088018053</v>
+        <v>93.516472903435599</v>
       </c>
       <c r="F13">
-        <v>213.60699571754427</v>
+        <v>213.84643600634277</v>
       </c>
       <c r="G13">
-        <v>39167493.692110002</v>
+        <v>412996.66060575511</v>
       </c>
       <c r="H13">
-        <v>3892.3274390618844</v>
+        <v>3802.0520976875391</v>
       </c>
       <c r="I13">
-        <v>69114.142772490959</v>
+        <v>50538.136221418536</v>
       </c>
       <c r="J13">
-        <v>73006.470211552849</v>
+        <v>54340.188319106077</v>
       </c>
       <c r="K13">
-        <v>28552751.890030041</v>
+        <v>759806.81784565607</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>2.0239316584546598</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -3616,34 +3616,34 @@
         <v>198</v>
       </c>
       <c r="C14">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D14">
-        <v>77.327539033980116</v>
+        <v>76.882401219990143</v>
       </c>
       <c r="E14">
-        <v>92.239719224970216</v>
+        <v>94.119304159897013</v>
       </c>
       <c r="F14">
-        <v>213.60877509308645</v>
+        <v>213.94727295958432</v>
       </c>
       <c r="G14">
-        <v>27404726.591215763</v>
+        <v>294721.32924690272</v>
       </c>
       <c r="H14">
-        <v>3893.88364496341</v>
+        <v>3738.9368108931644</v>
       </c>
       <c r="I14">
-        <v>65465.636407957456</v>
+        <v>49679.353951109857</v>
       </c>
       <c r="J14">
-        <v>69359.520052920867</v>
+        <v>53418.290762003024</v>
       </c>
       <c r="K14">
-        <v>15433649.899902737</v>
+        <v>239960.43600649043</v>
       </c>
       <c r="L14">
-        <v>2.0709541408829333</v>
+        <v>1.0418619697912928</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -3660,34 +3660,34 @@
         <v>198</v>
       </c>
       <c r="C15">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D15">
-        <v>77.237595875101178</v>
+        <v>76.382748570916831</v>
       </c>
       <c r="E15">
-        <v>92.2422619903341</v>
+        <v>94.947201493482765</v>
       </c>
       <c r="F15">
-        <v>213.61544947605765</v>
+        <v>214.0950470581098</v>
       </c>
       <c r="G15">
-        <v>15698071.224161567</v>
+        <v>192544.52885033062</v>
       </c>
       <c r="H15">
-        <v>3897.5854296230118</v>
+        <v>3685.1770729037594</v>
       </c>
       <c r="I15">
-        <v>61642.655948851236</v>
+        <v>48959.094414830528</v>
       </c>
       <c r="J15">
-        <v>65540.241378474253</v>
+        <v>52644.271487734288</v>
       </c>
       <c r="K15">
-        <v>19083506.425800905</v>
+        <v>229632.57674101918</v>
       </c>
       <c r="L15">
-        <v>1.722827088841117</v>
+        <v>0.77166202974835096</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -3704,34 +3704,34 @@
         <v>198</v>
       </c>
       <c r="C16">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D16">
-        <v>77.139955276245445</v>
+        <v>75.5386984651511</v>
       </c>
       <c r="E16">
-        <v>92.265016675483707</v>
+        <v>96.277180047247739</v>
       </c>
       <c r="F16">
-        <v>213.62935338112055</v>
+        <v>214.35360441788811</v>
       </c>
       <c r="G16">
-        <v>6951132.6338135079</v>
+        <v>115330.23842495929</v>
       </c>
       <c r="H16">
-        <v>3903.1289725452521</v>
+        <v>3649.14946210265</v>
       </c>
       <c r="I16">
-        <v>57992.098693566884</v>
+        <v>48404.008801521471</v>
       </c>
       <c r="J16">
-        <v>61895.227666112136</v>
+        <v>52053.158263624122</v>
       </c>
       <c r="K16">
-        <v>10890144.595265945</v>
+        <v>93228.400925830283</v>
       </c>
       <c r="L16">
-        <v>1.0434703568334416</v>
+        <v>0.3980087277248448</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -3748,34 +3748,34 @@
         <v>198</v>
       </c>
       <c r="C17">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D17">
-        <v>77.044646799862605</v>
+        <v>74.587978132867477</v>
       </c>
       <c r="E17">
-        <v>92.385479554054044</v>
+        <v>98.241373776313296</v>
       </c>
       <c r="F17">
-        <v>213.66513296879259</v>
+        <v>214.78778149924057</v>
       </c>
       <c r="G17">
-        <v>2361662.1662501153</v>
+        <v>67324.59276278688</v>
       </c>
       <c r="H17">
-        <v>3915.8632698802976</v>
+        <v>3646.2911700112359</v>
       </c>
       <c r="I17">
-        <v>54870.744463076197</v>
+        <v>48003.957543455632</v>
       </c>
       <c r="J17">
-        <v>58786.607732956494</v>
+        <v>51650.24871346687</v>
       </c>
       <c r="K17">
-        <v>3095784.1692538392</v>
+        <v>30621.086668782078</v>
       </c>
       <c r="L17">
-        <v>0.50914186024878239</v>
+        <v>0.1946535411018277</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -3792,34 +3792,34 @@
         <v>198</v>
       </c>
       <c r="C18">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D18">
-        <v>77.097555605314042</v>
+        <v>73.380057757803371</v>
       </c>
       <c r="E18">
-        <v>92.770029698657439</v>
+        <v>101.18400010290081</v>
       </c>
       <c r="F18">
-        <v>213.73356965247487</v>
+        <v>215.55437815413671</v>
       </c>
       <c r="G18">
-        <v>862544.78581207374</v>
+        <v>40881.108326016612</v>
       </c>
       <c r="H18">
-        <v>3888.1087342777114</v>
+        <v>3721.6524305159978</v>
       </c>
       <c r="I18">
-        <v>52389.084576891546</v>
+        <v>47702.536901863205</v>
       </c>
       <c r="J18">
-        <v>56277.193311169256</v>
+        <v>51424.189332379203</v>
       </c>
       <c r="K18">
-        <v>1903815.9795537712</v>
+        <v>27241.140677355015</v>
       </c>
       <c r="L18">
-        <v>0.31281864409153493</v>
+        <v>0.12358269348567942</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -3836,34 +3836,34 @@
         <v>198</v>
       </c>
       <c r="C19">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D19">
-        <v>77.136326010048407</v>
+        <v>71.33428982995305</v>
       </c>
       <c r="E19">
-        <v>93.516472903435599</v>
+        <v>106.10339215605562</v>
       </c>
       <c r="F19">
-        <v>213.84643600634277</v>
+        <v>217.05674869683418</v>
       </c>
       <c r="G19">
-        <v>412996.66060575511</v>
+        <v>26110.383554217857</v>
       </c>
       <c r="H19">
-        <v>3802.0520976875391</v>
+        <v>4157.9625207101708</v>
       </c>
       <c r="I19">
-        <v>50538.136221418536</v>
+        <v>47701.421315296582</v>
       </c>
       <c r="J19">
-        <v>54340.188319106077</v>
+        <v>51859.383836006753</v>
       </c>
       <c r="K19">
-        <v>547258.36054400436</v>
+        <v>10108.711199392315</v>
       </c>
       <c r="L19">
-        <v>0.16406125527560403</v>
+        <v>6.8409362328295878E-2</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -3880,40 +3880,40 @@
         <v>198</v>
       </c>
       <c r="C20">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D20">
-        <v>76.577804369601097</v>
+        <v>67.741425888894753</v>
       </c>
       <c r="E20">
-        <v>94.641130794904925</v>
+        <v>115.31625018496166</v>
       </c>
       <c r="F20">
-        <v>214.03849181822005</v>
+        <v>220.24751278454045</v>
       </c>
       <c r="G20">
-        <v>218876.1106177562</v>
+        <v>15205.998595947409</v>
       </c>
       <c r="H20">
-        <v>3698.9355324804246</v>
+        <v>5854.9714259797911</v>
       </c>
       <c r="I20">
-        <v>49181.249585299389</v>
+        <v>48881.671831767744</v>
       </c>
       <c r="J20">
-        <v>52880.185117779816</v>
+        <v>54736.643257747535</v>
       </c>
       <c r="K20">
-        <v>161694.08044098294</v>
+        <v>6778.7128503917293</v>
       </c>
       <c r="L20">
-        <v>7.7946942488050106E-2</v>
+        <v>6.093021636427233E-2</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -3924,34 +3924,34 @@
         <v>198</v>
       </c>
       <c r="C21">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D21">
-        <v>75.251462167724938</v>
+        <v>62.01187294543837</v>
       </c>
       <c r="E21">
-        <v>96.825772267181591</v>
+        <v>132.33110581511525</v>
       </c>
       <c r="F21">
-        <v>214.46762701246681</v>
+        <v>227.02177331604975</v>
       </c>
       <c r="G21">
-        <v>97508.500252968588</v>
+        <v>7998.416370336693</v>
       </c>
       <c r="H21">
-        <v>3646.0096006389717</v>
+        <v>11586.793617900938</v>
       </c>
       <c r="I21">
-        <v>48259.611740950582</v>
+        <v>51984.381145488151</v>
       </c>
       <c r="J21">
-        <v>51905.621341589555</v>
+        <v>63571.174763389092</v>
       </c>
       <c r="K21">
-        <v>40380.491476172494</v>
+        <v>2317.563643968746</v>
       </c>
       <c r="L21">
-        <v>2.5441043650419427E-2</v>
+        <v>0.10990622244486051</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -3968,40 +3968,40 @@
         <v>198</v>
       </c>
       <c r="C22">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D22">
-        <v>73.380057757803371</v>
+        <v>54.840984087652878</v>
       </c>
       <c r="E22">
-        <v>101.18400010290081</v>
+        <v>158.42698178879135</v>
       </c>
       <c r="F22">
-        <v>215.55437815413671</v>
+        <v>240.35366058461543</v>
       </c>
       <c r="G22">
-        <v>40881.108326016612</v>
+        <v>4684.4480143602987</v>
       </c>
       <c r="H22">
-        <v>3721.6524305159978</v>
+        <v>31312.112809600418</v>
       </c>
       <c r="I22">
-        <v>47702.536901863205</v>
+        <v>58037.67563205777</v>
       </c>
       <c r="J22">
-        <v>51424.189332379203</v>
+        <v>89349.788441658195</v>
       </c>
       <c r="K22">
-        <v>16462.20976513379</v>
+        <v>1507.8183269331219</v>
       </c>
       <c r="L22">
-        <v>8.4982708997406232E-4</v>
+        <v>0.31228878679200683</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -4012,34 +4012,34 @@
         <v>198</v>
       </c>
       <c r="C23">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D23">
-        <v>69.172410234351275</v>
+        <v>48.58247689163543</v>
       </c>
       <c r="E23">
-        <v>111.55994899122967</v>
+        <v>195.18649234688218</v>
       </c>
       <c r="F23">
-        <v>218.90861805560951</v>
+        <v>265.67957821474619</v>
       </c>
       <c r="G23">
-        <v>18671.965989980676</v>
+        <v>5828.7937698899777</v>
       </c>
       <c r="H23">
-        <v>5044.3211832936913</v>
+        <v>103262.52316490591</v>
       </c>
       <c r="I23">
-        <v>48275.534748277816</v>
+        <v>70008.59091159176</v>
       </c>
       <c r="J23">
-        <v>53319.85593157151</v>
+        <v>173271.11407649767</v>
       </c>
       <c r="K23">
-        <v>8397.6679304533172</v>
+        <v>723.92666844289226</v>
       </c>
       <c r="L23">
-        <v>8.7834395715866043E-2</v>
+        <v>1.0028026243649852</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4056,34 +4056,34 @@
         <v>198</v>
       </c>
       <c r="C24">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D24">
-        <v>75.357883371759314</v>
+        <v>74.433843372257556</v>
       </c>
       <c r="E24">
-        <v>75.864207869188405</v>
+        <v>76.801713118660189</v>
       </c>
       <c r="F24">
-        <v>208.44197271262857</v>
+        <v>208.54190084694665</v>
       </c>
       <c r="G24">
-        <v>25125833.909141243</v>
+        <v>598963.90905490529</v>
       </c>
       <c r="H24">
-        <v>3544.6821101630253</v>
+        <v>3370.9885866294562</v>
       </c>
       <c r="I24">
-        <v>45910.286300304142</v>
+        <v>45788.39204570635</v>
       </c>
       <c r="J24">
-        <v>49454.968410467169</v>
+        <v>49159.380632335808</v>
       </c>
       <c r="K24">
-        <v>12204191.584678845</v>
+        <v>140863.86605870776</v>
       </c>
       <c r="L24">
-        <v>2.6926064311290925</v>
+        <v>2.0070431885575912</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -4100,34 +4100,34 @@
         <v>198</v>
       </c>
       <c r="C25">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D25">
-        <v>75.328756059186617</v>
+        <v>73.885168532377421</v>
       </c>
       <c r="E25">
-        <v>75.869182950839061</v>
+        <v>77.240403371342239</v>
       </c>
       <c r="F25">
-        <v>208.44284144220291</v>
+        <v>208.59108771231499</v>
       </c>
       <c r="G25">
-        <v>17785985.446452599</v>
+        <v>348469.27311785339</v>
       </c>
       <c r="H25">
-        <v>3542.7169813846826</v>
+        <v>3322.1932314912378</v>
       </c>
       <c r="I25">
-        <v>45900.822744154364</v>
+        <v>45707.267609067654</v>
       </c>
       <c r="J25">
-        <v>49443.539725539049</v>
+        <v>49029.460840558895</v>
       </c>
       <c r="K25">
-        <v>10153327.631522875</v>
+        <v>122852.02337099631</v>
       </c>
       <c r="L25">
-        <v>2.2209109252830475</v>
+        <v>1.4533562715643638</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -4144,34 +4144,34 @@
         <v>198</v>
       </c>
       <c r="C26">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D26">
-        <v>75.253114454796091</v>
+        <v>73.15580565638831</v>
       </c>
       <c r="E26">
-        <v>75.885556455211827</v>
+        <v>77.975376647050908</v>
       </c>
       <c r="F26">
-        <v>208.44563327559374</v>
+        <v>208.6803726290274</v>
       </c>
       <c r="G26">
-        <v>10621854.72251608</v>
+        <v>206064.47046634727</v>
       </c>
       <c r="H26">
-        <v>3537.2428427428299</v>
+        <v>3284.5832223494317</v>
       </c>
       <c r="I26">
-        <v>45888.373665329353</v>
+        <v>45638.935092142303</v>
       </c>
       <c r="J26">
-        <v>49425.616508072184</v>
+        <v>48923.518314491732</v>
       </c>
       <c r="K26">
-        <v>8899992.9948967211</v>
+        <v>66491.535009530213</v>
       </c>
       <c r="L26">
-        <v>1.8152209949119844</v>
+        <v>0.80970440430523949</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -4188,34 +4188,34 @@
         <v>198</v>
       </c>
       <c r="C27">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D27">
-        <v>75.189567295631718</v>
+        <v>72.246056876708835</v>
       </c>
       <c r="E27">
-        <v>75.95591038476438</v>
+        <v>79.155259506787047</v>
       </c>
       <c r="F27">
-        <v>208.45492532561698</v>
+        <v>208.8413022218563</v>
       </c>
       <c r="G27">
-        <v>6250476.1250141868</v>
+        <v>125021.33540139238</v>
       </c>
       <c r="H27">
-        <v>3531.0996225271929</v>
+        <v>3249.2757157382325</v>
       </c>
       <c r="I27">
-        <v>45878.803577480263</v>
+        <v>45586.127519198366</v>
       </c>
       <c r="J27">
-        <v>49409.903200007459</v>
+        <v>48835.403234936595</v>
       </c>
       <c r="K27">
-        <v>3914209.6957676923</v>
+        <v>40119.230021755175</v>
       </c>
       <c r="L27">
-        <v>1.2170522944469038</v>
+        <v>0.4835210739141631</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -4232,34 +4232,34 @@
         <v>198</v>
       </c>
       <c r="C28">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D28">
-        <v>75.089880258550323</v>
+        <v>71.246615663483169</v>
       </c>
       <c r="E28">
-        <v>76.108569153751532</v>
+        <v>80.796401515766377</v>
       </c>
       <c r="F28">
-        <v>208.47438871204781</v>
+        <v>209.09725691351292</v>
       </c>
       <c r="G28">
-        <v>2892039.4015484126</v>
+        <v>76878.575047949838</v>
       </c>
       <c r="H28">
-        <v>3505.9003032943024</v>
+        <v>3212.4708697146134</v>
       </c>
       <c r="I28">
-        <v>45873.325815498691</v>
+        <v>45546.696385264135</v>
       </c>
       <c r="J28">
-        <v>49379.226118792991</v>
+        <v>48759.167254978747</v>
       </c>
       <c r="K28">
-        <v>1592137.739802154</v>
+        <v>19168.441686920316</v>
       </c>
       <c r="L28">
-        <v>0.8629006710318694</v>
+        <v>0.25172557367316872</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -4276,34 +4276,34 @@
         <v>198</v>
       </c>
       <c r="C29">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D29">
-        <v>74.928300218052584</v>
+        <v>69.970582927650895</v>
       </c>
       <c r="E29">
-        <v>76.364343052912261</v>
+        <v>83.025782483043031</v>
       </c>
       <c r="F29">
-        <v>208.50049982292279</v>
+        <v>209.5154056636847</v>
       </c>
       <c r="G29">
-        <v>1266171.8594096575</v>
+        <v>49137.393162051376</v>
       </c>
       <c r="H29">
-        <v>3446.4323372771701</v>
+        <v>3214.2525863998812</v>
       </c>
       <c r="I29">
-        <v>45855.696578389121</v>
+        <v>45533.379328031726</v>
       </c>
       <c r="J29">
-        <v>49302.12891566629</v>
+        <v>48747.631914431608</v>
       </c>
       <c r="K29">
-        <v>627776.87885119952</v>
+        <v>10140.132934863725</v>
       </c>
       <c r="L29">
-        <v>0.64359698581689462</v>
+        <v>0.14038382963512663</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -4320,34 +4320,34 @@
         <v>198</v>
       </c>
       <c r="C30">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D30">
-        <v>74.433843372257556</v>
+        <v>67.960675928283138</v>
       </c>
       <c r="E30">
-        <v>76.801713118660189</v>
+        <v>86.51712381557769</v>
       </c>
       <c r="F30">
-        <v>208.54190084694665</v>
+        <v>210.30656642112035</v>
       </c>
       <c r="G30">
-        <v>598963.90905490529</v>
+        <v>32625.684627609378</v>
       </c>
       <c r="H30">
-        <v>3370.9885866294562</v>
+        <v>3435.1894376235427</v>
       </c>
       <c r="I30">
-        <v>45788.39204570635</v>
+        <v>45608.60720357328</v>
       </c>
       <c r="J30">
-        <v>49159.380632335808</v>
+        <v>49043.796641196823</v>
       </c>
       <c r="K30">
-        <v>287770.72974234336</v>
+        <v>4313.2212840011107</v>
       </c>
       <c r="L30">
-        <v>0.44937348198323201</v>
+        <v>7.6069681189746524E-2</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -4364,40 +4364,40 @@
         <v>198</v>
       </c>
       <c r="C31">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D31">
-        <v>73.391367019778315</v>
+        <v>64.59309134831183</v>
       </c>
       <c r="E31">
-        <v>77.684674771280058</v>
+        <v>93.181952464656334</v>
       </c>
       <c r="F31">
-        <v>208.6450274378488</v>
+        <v>212.00068193290005</v>
       </c>
       <c r="G31">
-        <v>251014.31024132619</v>
+        <v>23118.794842413834</v>
       </c>
       <c r="H31">
-        <v>3299.0043714410317</v>
+        <v>4398.0513673364539</v>
       </c>
       <c r="I31">
-        <v>45662.025412194751</v>
+        <v>46046.456966029982</v>
       </c>
       <c r="J31">
-        <v>48961.029783635786</v>
+        <v>50444.508333366437</v>
       </c>
       <c r="K31">
-        <v>67555.51810665938</v>
+        <v>1568.7025697136655</v>
       </c>
       <c r="L31">
-        <v>0.22324243549233364</v>
+        <v>6.4428426755491444E-2</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -4408,34 +4408,34 @@
         <v>198</v>
       </c>
       <c r="C32">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D32">
-        <v>71.975984382335824</v>
+        <v>59.658534499695755</v>
       </c>
       <c r="E32">
-        <v>79.633882659641273</v>
+        <v>105.34535067686778</v>
       </c>
       <c r="F32">
-        <v>208.91083225733621</v>
+        <v>215.66473217678214</v>
       </c>
       <c r="G32">
-        <v>106854.60432581394</v>
+        <v>14844.363398392989</v>
       </c>
       <c r="H32">
-        <v>3237.736723263642</v>
+        <v>7479.5608203618931</v>
       </c>
       <c r="I32">
-        <v>45569.955802310389</v>
+        <v>47620.298328171441</v>
       </c>
       <c r="J32">
-        <v>48807.692525574028</v>
+        <v>55099.859148533331</v>
       </c>
       <c r="K32">
-        <v>33237.209760069607</v>
+        <v>1215.0244727208951</v>
       </c>
       <c r="L32">
-        <v>6.45423880230106E-2</v>
+        <v>0.12756237290998129</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -4452,40 +4452,40 @@
         <v>198</v>
       </c>
       <c r="C33">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D33">
-        <v>69.970582927650895</v>
+        <v>53.988592614911511</v>
       </c>
       <c r="E33">
-        <v>83.025782483043031</v>
+        <v>123.81657959972529</v>
       </c>
       <c r="F33">
-        <v>209.5154056636847</v>
+        <v>222.86631114977112</v>
       </c>
       <c r="G33">
-        <v>49137.393162051376</v>
+        <v>9191.5638570638712</v>
       </c>
       <c r="H33">
-        <v>3214.2525863998812</v>
+        <v>17242.901073320536</v>
       </c>
       <c r="I33">
-        <v>45533.379328031726</v>
+        <v>50932.658324234071</v>
       </c>
       <c r="J33">
-        <v>48747.631914431608</v>
+        <v>68175.559397554607</v>
       </c>
       <c r="K33">
-        <v>5520.806346299637</v>
+        <v>407.98956298661199</v>
       </c>
       <c r="L33">
-        <v>1.1614762725923014E-3</v>
+        <v>0.33593311094758954</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -4496,31 +4496,31 @@
         <v>198</v>
       </c>
       <c r="C34">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D34">
-        <v>65.826069615418305</v>
+        <v>49.177951397587591</v>
       </c>
       <c r="E34">
-        <v>90.478814946993651</v>
+        <v>148.91987871729484</v>
       </c>
       <c r="F34">
-        <v>211.28840895277509</v>
+        <v>236.29590274670585</v>
       </c>
       <c r="G34">
-        <v>25398.105360796915</v>
+        <v>7110.962512799757</v>
       </c>
       <c r="H34">
-        <v>3935.0222770163673</v>
+        <v>50370.281492854585</v>
       </c>
       <c r="I34">
-        <v>45833.877220626178</v>
+        <v>56837.90625327007</v>
       </c>
       <c r="J34">
-        <v>49768.899497642546</v>
+        <v>107208.18774612466</v>
       </c>
       <c r="K34">
-        <v>2888.9324699679596</v>
+        <v>395.02282280527209</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -4540,34 +4540,34 @@
         <v>198</v>
       </c>
       <c r="C35">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D35">
-        <v>79.049852035023832</v>
+        <v>77.919655753378393</v>
       </c>
       <c r="E35">
-        <v>73.201761670720444</v>
+        <v>73.686195856618639</v>
       </c>
       <c r="F35">
-        <v>207.65711169219782</v>
+        <v>207.7349677521598</v>
       </c>
       <c r="G35">
-        <v>22780202.366357069</v>
+        <v>716443.29542238091</v>
       </c>
       <c r="H35">
-        <v>3655.6512502972414</v>
+        <v>3516.2775659337203</v>
       </c>
       <c r="I35">
-        <v>45951.954532703247</v>
+        <v>45541.875490492181</v>
       </c>
       <c r="J35">
-        <v>49607.605783000487</v>
+        <v>49058.153056425901</v>
       </c>
       <c r="K35">
-        <v>9428646.6636677198</v>
+        <v>160755.10345596654</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>2.0111124527023576</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -4584,34 +4584,34 @@
         <v>198</v>
       </c>
       <c r="C36">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D36">
-        <v>79.055760258655823</v>
+        <v>77.245787181060905</v>
       </c>
       <c r="E36">
-        <v>73.208036710524652</v>
+        <v>73.996188433413209</v>
       </c>
       <c r="F36">
-        <v>207.65764575889659</v>
+        <v>207.77701894622174</v>
       </c>
       <c r="G36">
-        <v>17125073.282416265</v>
+        <v>401212.79515372968</v>
       </c>
       <c r="H36">
-        <v>3654.9129194599723</v>
+        <v>3478.2781776672928</v>
       </c>
       <c r="I36">
-        <v>45924.771703801154</v>
+        <v>45426.885371294375</v>
       </c>
       <c r="J36">
-        <v>49579.684623261128</v>
+        <v>48905.163548961667</v>
       </c>
       <c r="K36">
-        <v>7469990.8674559519</v>
+        <v>71434.640923805913</v>
       </c>
       <c r="L36">
-        <v>2.5172140065702595</v>
+        <v>1.0068833993943556</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -4628,34 +4628,34 @@
         <v>198</v>
       </c>
       <c r="C37">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D37">
-        <v>79.057496634199182</v>
+        <v>76.4598843729555</v>
       </c>
       <c r="E37">
-        <v>73.224915107238132</v>
+        <v>74.636437099413953</v>
       </c>
       <c r="F37">
-        <v>207.65969948305201</v>
+        <v>207.85845742180098</v>
       </c>
       <c r="G37">
-        <v>10210403.453806432</v>
+        <v>230857.6113619282</v>
       </c>
       <c r="H37">
-        <v>3651.9291884708723</v>
+        <v>3453.5020978079738</v>
       </c>
       <c r="I37">
-        <v>45886.479794471263</v>
+        <v>45325.894124185659</v>
       </c>
       <c r="J37">
-        <v>49538.408982942135</v>
+        <v>48779.396221993637</v>
       </c>
       <c r="K37">
-        <v>5512926.7891564742</v>
+        <v>46584.960846998867</v>
       </c>
       <c r="L37">
-        <v>1.9665847171256092</v>
+        <v>0.60914813835668835</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -4672,34 +4672,34 @@
         <v>198</v>
       </c>
       <c r="C38">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D38">
-        <v>79.058321833234515</v>
+        <v>75.584802365887128</v>
       </c>
       <c r="E38">
-        <v>73.270811027212261</v>
+        <v>75.734160320216759</v>
       </c>
       <c r="F38">
-        <v>207.66589727880461</v>
+        <v>208.00264115711744</v>
       </c>
       <c r="G38">
-        <v>5903692.2842046181</v>
+        <v>136598.83532419245</v>
       </c>
       <c r="H38">
-        <v>3642.9285258830378</v>
+        <v>3443.4495047997248</v>
       </c>
       <c r="I38">
-        <v>45834.211598672337</v>
+        <v>45233.703940924686</v>
       </c>
       <c r="J38">
-        <v>49477.140124555372</v>
+        <v>48677.153445724412</v>
       </c>
       <c r="K38">
-        <v>3605447.2480554432</v>
+        <v>24047.976584732907</v>
       </c>
       <c r="L38">
-        <v>1.5168697999030794</v>
+        <v>0.33361303238508944</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -4716,34 +4716,34 @@
         <v>198</v>
       </c>
       <c r="C39">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D39">
-        <v>78.904424222817795</v>
+        <v>74.62177931810821</v>
       </c>
       <c r="E39">
-        <v>73.353760280914187</v>
+        <v>77.295426842782106</v>
       </c>
       <c r="F39">
-        <v>207.68186150253223</v>
+        <v>208.22638459806305</v>
       </c>
       <c r="G39">
-        <v>3772351.5868841494</v>
+        <v>81377.757860148646</v>
       </c>
       <c r="H39">
-        <v>3633.3128579723279</v>
+        <v>3446.010726830631</v>
       </c>
       <c r="I39">
-        <v>45767.406697113875</v>
+        <v>45143.520409303339</v>
       </c>
       <c r="J39">
-        <v>49400.719555086202</v>
+        <v>48589.53113613397</v>
       </c>
       <c r="K39">
-        <v>941371.23219208408</v>
+        <v>8326.8566943103979</v>
       </c>
       <c r="L39">
-        <v>1.0681199575840237</v>
+        <v>0.15589533622267066</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -4760,34 +4760,34 @@
         <v>198</v>
       </c>
       <c r="C40">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D40">
-        <v>78.570863678476655</v>
+        <v>73.426759968431142</v>
       </c>
       <c r="E40">
-        <v>73.476434126159759</v>
+        <v>79.309150779515178</v>
       </c>
       <c r="F40">
-        <v>207.70451376612849</v>
+        <v>208.56579122551352</v>
       </c>
       <c r="G40">
-        <v>1798547.2464873942</v>
+        <v>50356.633379202118</v>
       </c>
       <c r="H40">
-        <v>3587.1662725100782</v>
+        <v>3493.9525840197916</v>
       </c>
       <c r="I40">
-        <v>45677.810970429331</v>
+        <v>45058.861724048249</v>
       </c>
       <c r="J40">
-        <v>49264.977242939407</v>
+        <v>48552.814308068038</v>
       </c>
       <c r="K40">
-        <v>541362.92870982829</v>
+        <v>4826.7795135880388</v>
       </c>
       <c r="L40">
-        <v>0.81025116388164209</v>
+        <v>8.9550943305548442E-2</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -4804,40 +4804,40 @@
         <v>198</v>
       </c>
       <c r="C41">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D41">
-        <v>77.919655753378393</v>
+        <v>71.624998819019936</v>
       </c>
       <c r="E41">
-        <v>73.686195856618639</v>
+        <v>82.046270087437591</v>
       </c>
       <c r="F41">
-        <v>207.7349677521598</v>
+        <v>209.15437478935019</v>
       </c>
       <c r="G41">
-        <v>716443.29542238091</v>
+        <v>32388.849713649612</v>
       </c>
       <c r="H41">
-        <v>3516.2775659337203</v>
+        <v>3739.6831537633739</v>
       </c>
       <c r="I41">
-        <v>45541.875490492181</v>
+        <v>45025.632734032966</v>
       </c>
       <c r="J41">
-        <v>49058.153056425901</v>
+        <v>48765.315887796343</v>
       </c>
       <c r="K41">
-        <v>162075.71111369494</v>
+        <v>3387.4943086734811</v>
       </c>
       <c r="L41">
-        <v>0.52637758446411664</v>
+        <v>5.9927431432572384E-2</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -4848,34 +4848,34 @@
         <v>198</v>
       </c>
       <c r="C42">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D42">
-        <v>76.75794671693339</v>
+        <v>68.720570877290854</v>
       </c>
       <c r="E42">
-        <v>74.377358656304409</v>
+        <v>86.534435632893377</v>
       </c>
       <c r="F42">
-        <v>207.82450669042751</v>
+        <v>210.36324193540219</v>
       </c>
       <c r="G42">
-        <v>281194.38984917098</v>
+        <v>22303.099160763912</v>
       </c>
       <c r="H42">
-        <v>3462.0191844467518</v>
+        <v>4618.4677995906859</v>
       </c>
       <c r="I42">
-        <v>45359.877685693456</v>
+        <v>45229.243074797705</v>
       </c>
       <c r="J42">
-        <v>48821.896870140205</v>
+        <v>49847.710874388387</v>
       </c>
       <c r="K42">
-        <v>90958.705491340617</v>
+        <v>2119.4145873341245</v>
       </c>
       <c r="L42">
-        <v>0.27572157972631389</v>
+        <v>6.1611041223698586E-2</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -4892,34 +4892,34 @@
         <v>198</v>
       </c>
       <c r="C43">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D43">
-        <v>75.271762004504993</v>
+        <v>64.535711104656713</v>
       </c>
       <c r="E43">
-        <v>76.187914800783304</v>
+        <v>96.000267240331709</v>
       </c>
       <c r="F43">
-        <v>208.06564949718677</v>
+        <v>212.98478606959756</v>
       </c>
       <c r="G43">
-        <v>113160.96822881812</v>
+        <v>14695.966815726451</v>
       </c>
       <c r="H43">
-        <v>3439.7737309809536</v>
+        <v>7246.8578161561991</v>
       </c>
       <c r="I43">
-        <v>45202.013781893191</v>
+        <v>46228.040738021933</v>
       </c>
       <c r="J43">
-        <v>48641.787512874143</v>
+        <v>53474.898554178129</v>
       </c>
       <c r="K43">
-        <v>25223.609846429728</v>
+        <v>1066.4745990061831</v>
       </c>
       <c r="L43">
-        <v>9.060978257662676E-2</v>
+        <v>0.12408941404025739</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -4936,40 +4936,40 @@
         <v>198</v>
       </c>
       <c r="C44">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D44">
-        <v>73.426759968431142</v>
+        <v>59.829936789319326</v>
       </c>
       <c r="E44">
-        <v>79.309150779515178</v>
+        <v>111.44631019602784</v>
       </c>
       <c r="F44">
-        <v>208.56579122551352</v>
+        <v>218.20767922354096</v>
       </c>
       <c r="G44">
-        <v>50356.633379202118</v>
+        <v>9359.2505510809879</v>
       </c>
       <c r="H44">
-        <v>3493.9525840197916</v>
+        <v>15179.835924349363</v>
       </c>
       <c r="I44">
-        <v>45058.861724048249</v>
+        <v>48672.261495887687</v>
       </c>
       <c r="J44">
-        <v>48552.814308068038</v>
+        <v>63852.097420237049</v>
       </c>
       <c r="K44">
-        <v>5494.6043568566156</v>
+        <v>327.40011985581646</v>
       </c>
       <c r="L44">
-        <v>1.4052600139454214E-3</v>
+        <v>0.34015731990736481</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -4980,34 +4980,34 @@
         <v>198</v>
       </c>
       <c r="C45">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D45">
-        <v>69.794172543936256</v>
+        <v>55.937367386806862</v>
       </c>
       <c r="E45">
-        <v>84.732834059003991</v>
+        <v>132.70843245668809</v>
       </c>
       <c r="F45">
-        <v>209.86054178860397</v>
+        <v>228.16669916130579</v>
       </c>
       <c r="G45">
-        <v>24841.752985655698</v>
+        <v>7081.2759979854482</v>
       </c>
       <c r="H45">
-        <v>4205.7453143407374</v>
+        <v>40967.369045186249</v>
       </c>
       <c r="I45">
-        <v>45114.62841672777</v>
+        <v>53060.441817931227</v>
       </c>
       <c r="J45">
-        <v>49320.37373106851</v>
+        <v>94027.810863117484</v>
       </c>
       <c r="K45">
-        <v>2817.7536283442832</v>
+        <v>245.03272295230815</v>
       </c>
       <c r="L45">
-        <v>0.72768830734968581</v>
+        <v>1</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -5024,34 +5024,34 @@
         <v>198</v>
       </c>
       <c r="C46">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D46">
-        <v>82.026163782449387</v>
+        <v>81.373333349110723</v>
       </c>
       <c r="E46">
-        <v>75.623544525989104</v>
+        <v>76.088814272539608</v>
       </c>
       <c r="F46">
-        <v>208.12162144758801</v>
+        <v>208.19848985869035</v>
       </c>
       <c r="G46">
-        <v>23299716.612307511</v>
+        <v>608736.40584117931</v>
       </c>
       <c r="H46">
-        <v>5214.7008221549977</v>
+        <v>5049.6635716921865</v>
       </c>
       <c r="I46">
-        <v>46197.080013535764</v>
+        <v>45960.359699210967</v>
       </c>
       <c r="J46">
-        <v>51411.780835690763</v>
+        <v>51010.023270903155</v>
       </c>
       <c r="K46">
-        <v>7810949.6674360316</v>
+        <v>127197.7492053365</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>2.0152526815345539</v>
       </c>
       <c r="M46">
         <v>1</v>
@@ -5068,34 +5068,34 @@
         <v>198</v>
       </c>
       <c r="C47">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D47">
-        <v>82.029397133345341</v>
+        <v>80.893434067919472</v>
       </c>
       <c r="E47">
-        <v>75.62807796759239</v>
+        <v>76.360526639475125</v>
       </c>
       <c r="F47">
-        <v>208.12208127588335</v>
+        <v>208.23128331049713</v>
       </c>
       <c r="G47">
-        <v>17507457.386827961</v>
+        <v>358937.68332666589</v>
       </c>
       <c r="H47">
-        <v>5216.8304014147052</v>
+        <v>4978.9337432337952</v>
       </c>
       <c r="I47">
-        <v>46177.336031206425</v>
+        <v>45867.785014110195</v>
       </c>
       <c r="J47">
-        <v>51394.166432621132</v>
+        <v>50846.718757343988</v>
       </c>
       <c r="K47">
-        <v>6327378.9618687639</v>
+        <v>89588.663829454556</v>
       </c>
       <c r="L47">
-        <v>2.5454763006599501</v>
+        <v>1.3000305952458402</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -5112,34 +5112,34 @@
         <v>198</v>
       </c>
       <c r="C48">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D48">
-        <v>82.022197105924207</v>
+        <v>80.309731268831015</v>
       </c>
       <c r="E48">
-        <v>75.640808690301682</v>
+        <v>76.818544748556178</v>
       </c>
       <c r="F48">
-        <v>208.12447251926358</v>
+        <v>208.2884124250551</v>
       </c>
       <c r="G48">
-        <v>11131430.400961766</v>
+        <v>211943.14967531094</v>
       </c>
       <c r="H48">
-        <v>5221.2264696560278</v>
+        <v>4916.0605723117551</v>
       </c>
       <c r="I48">
-        <v>46149.602184591153</v>
+        <v>45777.165804665274</v>
       </c>
       <c r="J48">
-        <v>51370.828654247183</v>
+        <v>50693.226376977029</v>
       </c>
       <c r="K48">
-        <v>4776848.2414390435</v>
+        <v>32542.070628007281</v>
       </c>
       <c r="L48">
-        <v>2.0522026830220708</v>
+        <v>0.6029529631813535</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -5156,34 +5156,34 @@
         <v>198</v>
       </c>
       <c r="C49">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D49">
-        <v>82.024770295544727</v>
+        <v>79.536326842534663</v>
       </c>
       <c r="E49">
-        <v>75.670963801822609</v>
+        <v>77.526585610566414</v>
       </c>
       <c r="F49">
-        <v>208.13091042787116</v>
+        <v>208.38726142068853</v>
       </c>
       <c r="G49">
-        <v>6028123.6625166759</v>
+        <v>125332.02643167615</v>
       </c>
       <c r="H49">
-        <v>5220.6544261179615</v>
+        <v>4858.848450160388</v>
       </c>
       <c r="I49">
-        <v>46122.920244492714</v>
+        <v>45688.502735265589</v>
       </c>
       <c r="J49">
-        <v>51343.574670610673</v>
+        <v>50547.351185425978</v>
       </c>
       <c r="K49">
-        <v>2391376.0679315622</v>
+        <v>29770.622576305192</v>
       </c>
       <c r="L49">
-        <v>1.5032087249064714</v>
+        <v>0.43395686129775657</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -5200,34 +5200,34 @@
         <v>198</v>
       </c>
       <c r="C50">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D50">
-        <v>81.958555664565338</v>
+        <v>78.637985233265937</v>
       </c>
       <c r="E50">
-        <v>75.737218099188368</v>
+        <v>78.534796898975912</v>
       </c>
       <c r="F50">
-        <v>208.14809321567654</v>
+        <v>208.53431166089428</v>
       </c>
       <c r="G50">
-        <v>3219136.0680096764</v>
+        <v>75513.28847611633</v>
       </c>
       <c r="H50">
-        <v>5206.7182696059499</v>
+        <v>4809.1493556011528</v>
       </c>
       <c r="I50">
-        <v>46103.406654511607</v>
+        <v>45598.174883927481</v>
       </c>
       <c r="J50">
-        <v>51310.124924117554</v>
+        <v>50407.324239528636</v>
       </c>
       <c r="K50">
-        <v>1411259.4620022746</v>
+        <v>13646.211094739869</v>
       </c>
       <c r="L50">
-        <v>1.2272419056070341</v>
+        <v>0.22112539938857767</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -5244,34 +5244,34 @@
         <v>198</v>
       </c>
       <c r="C51">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D51">
-        <v>81.817183592615734</v>
+        <v>77.431857459457945</v>
       </c>
       <c r="E51">
-        <v>75.859046420385283</v>
+        <v>80.07905402848229</v>
       </c>
       <c r="F51">
-        <v>208.17016130680759</v>
+        <v>208.77543374381762</v>
       </c>
       <c r="G51">
-        <v>1381493.7841270964</v>
+        <v>48218.535681814858</v>
       </c>
       <c r="H51">
-        <v>5156.6641021579953</v>
+        <v>4814.7754093054627</v>
       </c>
       <c r="I51">
-        <v>46062.084481515318</v>
+        <v>45473.288097412544</v>
       </c>
       <c r="J51">
-        <v>51218.74858367331</v>
+        <v>50288.063506718005</v>
       </c>
       <c r="K51">
-        <v>522061.00754611794</v>
+        <v>6264.2010972236721</v>
       </c>
       <c r="L51">
-        <v>0.95310323821815046</v>
+        <v>0.11505806642613528</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -5288,40 +5288,40 @@
         <v>198</v>
       </c>
       <c r="C52">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D52">
-        <v>81.373333349110723</v>
+        <v>75.5325464723132</v>
       </c>
       <c r="E52">
-        <v>76.088814272539608</v>
+        <v>82.661147594946499</v>
       </c>
       <c r="F52">
-        <v>208.19848985869035</v>
+        <v>209.26636466038931</v>
       </c>
       <c r="G52">
-        <v>608736.40584117931</v>
+        <v>32246.162737942508</v>
       </c>
       <c r="H52">
-        <v>5049.6635716921865</v>
+        <v>5064.7611848081524</v>
       </c>
       <c r="I52">
-        <v>45960.359699210967</v>
+        <v>45399.220646377071</v>
       </c>
       <c r="J52">
-        <v>51010.023270903155</v>
+        <v>50463.981831185221</v>
       </c>
       <c r="K52">
-        <v>206784.62050103358</v>
+        <v>2760.3063433026841</v>
       </c>
       <c r="L52">
-        <v>0.69378282343024755</v>
+        <v>6.4606577580540628E-2</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -5332,34 +5332,34 @@
         <v>198</v>
       </c>
       <c r="C53">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D53">
-        <v>80.494711925680591</v>
+        <v>72.462185675270192</v>
       </c>
       <c r="E53">
-        <v>76.640622542626602</v>
+        <v>87.307092781287423</v>
       </c>
       <c r="F53">
-        <v>208.26633938663298</v>
+        <v>210.38390748273881</v>
       </c>
       <c r="G53">
-        <v>258483.9709156249</v>
+        <v>22896.545040971974</v>
       </c>
       <c r="H53">
-        <v>4941.1856850249706</v>
+        <v>6064.7620681837634</v>
       </c>
       <c r="I53">
-        <v>45808.114340975524</v>
+        <v>45593.930725454542</v>
       </c>
       <c r="J53">
-        <v>50749.300026000492</v>
+        <v>51658.692793638307</v>
       </c>
       <c r="K53">
-        <v>60005.705283936361</v>
+        <v>1625.1815768293773</v>
       </c>
       <c r="L53">
-        <v>0.42791956333204828</v>
+        <v>6.5352765171794114E-2</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -5376,34 +5376,34 @@
         <v>198</v>
       </c>
       <c r="C54">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D54">
-        <v>79.287801197996245</v>
+        <v>68.086636531562604</v>
       </c>
       <c r="E54">
-        <v>77.826954465588869</v>
+        <v>96.152045325878277</v>
       </c>
       <c r="F54">
-        <v>208.42982408145789</v>
+        <v>212.87572050844688</v>
       </c>
       <c r="G54">
-        <v>103455.71385371272</v>
+        <v>15865.82696466044</v>
       </c>
       <c r="H54">
-        <v>4836.0856530523788</v>
+        <v>9035.5793549065893</v>
       </c>
       <c r="I54">
-        <v>45658.641032338077</v>
+        <v>46482.130970125596</v>
       </c>
       <c r="J54">
-        <v>50494.726685390458</v>
+        <v>55517.710325032182</v>
       </c>
       <c r="K54">
-        <v>14657.172615282961</v>
+        <v>718.72445856599609</v>
       </c>
       <c r="L54">
-        <v>0.18890580740575014</v>
+        <v>0.12804585447665176</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -5420,40 +5420,40 @@
         <v>198</v>
       </c>
       <c r="C55">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D55">
-        <v>77.431857459457945</v>
+        <v>63.133311485439648</v>
       </c>
       <c r="E55">
-        <v>80.07905402848229</v>
+        <v>110.87759631128206</v>
       </c>
       <c r="F55">
-        <v>208.77543374381762</v>
+        <v>217.86553750403564</v>
       </c>
       <c r="G55">
-        <v>48218.535681814858</v>
+        <v>10213.45058028795</v>
       </c>
       <c r="H55">
-        <v>4814.7754093054627</v>
+        <v>17652.553966283522</v>
       </c>
       <c r="I55">
-        <v>45473.288097412544</v>
+        <v>48905.78901993094</v>
       </c>
       <c r="J55">
-        <v>50288.063506718005</v>
+        <v>66558.342986214469</v>
       </c>
       <c r="K55">
-        <v>8195.5869251459571</v>
+        <v>551.37743197619079</v>
       </c>
       <c r="L55">
-        <v>1.7947654818739689E-3</v>
+        <v>0.35057749488060191</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -5464,34 +5464,34 @@
         <v>198</v>
       </c>
       <c r="C56">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D56">
-        <v>73.649124426664244</v>
+        <v>58.979175099750464</v>
       </c>
       <c r="E56">
-        <v>85.437674648274978</v>
+        <v>131.42341739117498</v>
       </c>
       <c r="F56">
-        <v>209.90469327871045</v>
+        <v>227.34638797992866</v>
       </c>
       <c r="G56">
-        <v>25413.549883197447</v>
+        <v>7631.489631255723</v>
       </c>
       <c r="H56">
-        <v>5593.6699522704148</v>
+        <v>44382.672286569948</v>
       </c>
       <c r="I56">
-        <v>45485.268706850256</v>
+        <v>53238.69209249624</v>
       </c>
       <c r="J56">
-        <v>51078.938659120671</v>
+        <v>97621.364379066188</v>
       </c>
       <c r="K56">
-        <v>1831.7016973185978</v>
+        <v>228.41798033908191</v>
       </c>
       <c r="L56">
-        <v>0.70380257740231</v>
+        <v>1</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -5508,34 +5508,34 @@
         <v>198</v>
       </c>
       <c r="C57">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D57">
-        <v>81.285201358986271</v>
+        <v>80.324288140805749</v>
       </c>
       <c r="E57">
-        <v>73.395324049711746</v>
+        <v>74.028814332326576</v>
       </c>
       <c r="F57">
-        <v>208.1153340787836</v>
+        <v>208.18494988744283</v>
       </c>
       <c r="G57">
-        <v>21643439.202955514</v>
+        <v>647019.68479627802</v>
       </c>
       <c r="H57">
-        <v>4336.7757351725204</v>
+        <v>4213.6232288330029</v>
       </c>
       <c r="I57">
-        <v>45973.578247873469</v>
+        <v>45854.969388646554</v>
       </c>
       <c r="J57">
-        <v>50310.353983045992</v>
+        <v>50068.59261747956</v>
       </c>
       <c r="K57">
-        <v>7509020.0985761629</v>
+        <v>159368.07010304031</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>2.018105812263042</v>
       </c>
       <c r="M57">
         <v>1</v>
@@ -5552,34 +5552,34 @@
         <v>198</v>
       </c>
       <c r="C58">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D58">
-        <v>81.308001309035305</v>
+        <v>79.762687061705819</v>
       </c>
       <c r="E58">
-        <v>73.404278175595721</v>
+        <v>74.390745128648589</v>
       </c>
       <c r="F58">
-        <v>208.11581495609673</v>
+        <v>208.21793065233192</v>
       </c>
       <c r="G58">
-        <v>16399963.711532798</v>
+        <v>373987.87835695036</v>
       </c>
       <c r="H58">
-        <v>4338.1139418730991</v>
+        <v>4153.4368755648838</v>
       </c>
       <c r="I58">
-        <v>45968.712008273476</v>
+        <v>45766.737005777373</v>
       </c>
       <c r="J58">
-        <v>50306.825950146573</v>
+        <v>49920.173881342256</v>
       </c>
       <c r="K58">
-        <v>6606346.0517900558</v>
+        <v>62782.983339226768</v>
       </c>
       <c r="L58">
-        <v>2.633795773224874</v>
+        <v>0.98120817366147395</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -5596,34 +5596,34 @@
         <v>198</v>
       </c>
       <c r="C59">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D59">
-        <v>81.371713350147701</v>
+        <v>79.022453950199235</v>
       </c>
       <c r="E59">
-        <v>73.438101366069716</v>
+        <v>74.950319498810515</v>
       </c>
       <c r="F59">
-        <v>208.11779442497766</v>
+        <v>208.27771746886299</v>
       </c>
       <c r="G59">
-        <v>9936470.7089825477</v>
+        <v>220447.07625269709</v>
       </c>
       <c r="H59">
-        <v>4339.3042268260588</v>
+        <v>4094.8017364611023</v>
       </c>
       <c r="I59">
-        <v>45965.530693199253</v>
+        <v>45682.035470761322</v>
       </c>
       <c r="J59">
-        <v>50304.834920025314</v>
+        <v>49776.837207222423</v>
       </c>
       <c r="K59">
-        <v>4162943.008533203</v>
+        <v>30663.022183369703</v>
       </c>
       <c r="L59">
-        <v>2.007419650146832</v>
+        <v>0.5361647502852489</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -5640,34 +5640,34 @@
         <v>198</v>
       </c>
       <c r="C60">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D60">
-        <v>81.28039552243375</v>
+        <v>78.176205311718633</v>
       </c>
       <c r="E60">
-        <v>73.482134642691094</v>
+        <v>75.783808076204949</v>
       </c>
       <c r="F60">
-        <v>208.12497708396046</v>
+        <v>208.37397180484854</v>
       </c>
       <c r="G60">
-        <v>5678715.1004885519</v>
+        <v>132035.69296219654</v>
       </c>
       <c r="H60">
-        <v>4340.7316441651328</v>
+        <v>4033.776170057753</v>
       </c>
       <c r="I60">
-        <v>45965.154016331973</v>
+        <v>45582.382836932295</v>
       </c>
       <c r="J60">
-        <v>50305.885660497108</v>
+        <v>49616.159006990049</v>
       </c>
       <c r="K60">
-        <v>2576465.2107463568</v>
+        <v>30647.647515795099</v>
       </c>
       <c r="L60">
-        <v>1.6001644504935357</v>
+        <v>0.39420413050715453</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -5684,34 +5684,34 @@
         <v>198</v>
       </c>
       <c r="C61">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D61">
-        <v>81.153442913592144</v>
+        <v>77.148376155808421</v>
       </c>
       <c r="E61">
-        <v>73.584904083611576</v>
+        <v>76.900774656166277</v>
       </c>
       <c r="F61">
-        <v>208.14102665839826</v>
+        <v>208.51932350594694</v>
       </c>
       <c r="G61">
-        <v>3456340.4051455506</v>
+        <v>78853.154098006693</v>
       </c>
       <c r="H61">
-        <v>4329.2029807366916</v>
+        <v>3971.4267116485939</v>
       </c>
       <c r="I61">
-        <v>45963.856829475844</v>
+        <v>45453.605362477749</v>
       </c>
       <c r="J61">
-        <v>50293.059810212537</v>
+        <v>49425.032074126342</v>
       </c>
       <c r="K61">
-        <v>1440492.997041407</v>
+        <v>8471.3069732451913</v>
       </c>
       <c r="L61">
-        <v>1.3336284623512764</v>
+        <v>0.16739070595260652</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -5728,34 +5728,34 @@
         <v>198</v>
       </c>
       <c r="C62">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D62">
-        <v>80.896436548056244</v>
+        <v>75.676688565005321</v>
       </c>
       <c r="E62">
-        <v>73.73936582633813</v>
+        <v>78.474028155676351</v>
       </c>
       <c r="F62">
-        <v>208.15899142457826</v>
+        <v>208.76825359979117</v>
       </c>
       <c r="G62">
-        <v>1594648.7967289591</v>
+        <v>49681.709289034792</v>
       </c>
       <c r="H62">
-        <v>4284.0985185681338</v>
+        <v>3959.9028700986087</v>
       </c>
       <c r="I62">
-        <v>45941.558931563311</v>
+        <v>45317.977342435763</v>
       </c>
       <c r="J62">
-        <v>50225.657450131446</v>
+        <v>49277.880212534372</v>
       </c>
       <c r="K62">
-        <v>528905.00165119779</v>
+        <v>3778.1055990263249</v>
       </c>
       <c r="L62">
-        <v>1.0608048989996015</v>
+        <v>8.8943800206086138E-2</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -5772,40 +5772,40 @@
         <v>198</v>
       </c>
       <c r="C63">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D63">
-        <v>80.324288140805749</v>
+        <v>73.300161373667919</v>
       </c>
       <c r="E63">
-        <v>74.028814332326576</v>
+        <v>81.131579004371503</v>
       </c>
       <c r="F63">
-        <v>208.18494988744283</v>
+        <v>209.29982672609884</v>
       </c>
       <c r="G63">
-        <v>647019.68479627802</v>
+        <v>32463.119649426484</v>
       </c>
       <c r="H63">
-        <v>4213.6232288330029</v>
+        <v>4180.203177932307</v>
       </c>
       <c r="I63">
-        <v>45854.969388646554</v>
+        <v>45246.504372253024</v>
       </c>
       <c r="J63">
-        <v>50068.59261747956</v>
+        <v>49426.707550185332</v>
       </c>
       <c r="K63">
-        <v>126402.83052517528</v>
+        <v>2387.7138104851574</v>
       </c>
       <c r="L63">
-        <v>0.81123167324349954</v>
+        <v>5.670485307671351E-2</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -5816,34 +5816,34 @@
         <v>198</v>
       </c>
       <c r="C64">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D64">
-        <v>79.285555721128858</v>
+        <v>69.73637928047944</v>
       </c>
       <c r="E64">
-        <v>74.74283272393545</v>
+        <v>86.5429282763684</v>
       </c>
       <c r="F64">
-        <v>208.25453955773634</v>
+        <v>210.53342330649872</v>
       </c>
       <c r="G64">
-        <v>256465.89227112976</v>
+        <v>22896.132936818703</v>
       </c>
       <c r="H64">
-        <v>4110.4523606796893</v>
+        <v>5091.0151592332713</v>
       </c>
       <c r="I64">
-        <v>45710.589401100406</v>
+        <v>45456.671463043007</v>
       </c>
       <c r="J64">
-        <v>49821.041761780092</v>
+        <v>50547.686622276276</v>
       </c>
       <c r="K64">
-        <v>41614.475706355421</v>
+        <v>742.27364436029757</v>
       </c>
       <c r="L64">
-        <v>0.54210696196620012</v>
+        <v>5.708336130590886E-2</v>
       </c>
       <c r="M64">
         <v>0</v>
@@ -5860,34 +5860,34 @@
         <v>198</v>
       </c>
       <c r="C65">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D65">
-        <v>77.849288580115754</v>
+        <v>64.945213375366009</v>
       </c>
       <c r="E65">
-        <v>76.109886794213949</v>
+        <v>97.16591390807055</v>
       </c>
       <c r="F65">
-        <v>208.41520876042387</v>
+        <v>213.29802434587378</v>
       </c>
       <c r="G65">
-        <v>106852.57349051344</v>
+        <v>15125.462428908035</v>
       </c>
       <c r="H65">
-        <v>4005.2051222293658</v>
+        <v>7763.7994947112165</v>
       </c>
       <c r="I65">
-        <v>45539.81994064898</v>
+        <v>46597.385662150053</v>
       </c>
       <c r="J65">
-        <v>49545.025062878347</v>
+        <v>54361.185156861269</v>
       </c>
       <c r="K65">
-        <v>9572.504559649964</v>
+        <v>452.69383572688639</v>
       </c>
       <c r="L65">
-        <v>0.26358289277209818</v>
+        <v>0.13044069932096017</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -5904,40 +5904,40 @@
         <v>198</v>
       </c>
       <c r="C66">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D66">
-        <v>75.676688565005321</v>
+        <v>59.733774436386291</v>
       </c>
       <c r="E66">
-        <v>78.474028155676351</v>
+        <v>112.75649227485421</v>
       </c>
       <c r="F66">
-        <v>208.76825359979117</v>
+        <v>218.67867313772948</v>
       </c>
       <c r="G66">
-        <v>49681.709289034792</v>
+        <v>9609.2688279088397</v>
       </c>
       <c r="H66">
-        <v>3959.9028700986087</v>
+        <v>15451.973436505918</v>
       </c>
       <c r="I66">
-        <v>45317.977342435763</v>
+        <v>49124.613455592531</v>
       </c>
       <c r="J66">
-        <v>49277.880212534372</v>
+        <v>64576.58689209845</v>
       </c>
       <c r="K66">
-        <v>11914.193464255941</v>
+        <v>844.99376653944762</v>
       </c>
       <c r="L66">
-        <v>2.507711574251178E-3</v>
+        <v>0.3581967897650693</v>
       </c>
       <c r="M66">
         <v>0</v>
       </c>
       <c r="N66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -5948,34 +5948,34 @@
         <v>198</v>
       </c>
       <c r="C67">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D67">
-        <v>71.031077230495782</v>
+        <v>55.436640667174494</v>
       </c>
       <c r="E67">
-        <v>84.278422954177231</v>
+        <v>133.40116481994403</v>
       </c>
       <c r="F67">
-        <v>210.00752095524339</v>
+        <v>228.4869939206443</v>
       </c>
       <c r="G67">
-        <v>25387.075967160647</v>
+        <v>7214.3114924201036</v>
       </c>
       <c r="H67">
-        <v>4663.1722957981574</v>
+        <v>39459.024708876539</v>
       </c>
       <c r="I67">
-        <v>45335.384135970598</v>
+        <v>53490.599883732153</v>
       </c>
       <c r="J67">
-        <v>49998.556431768753</v>
+        <v>92949.624592608685</v>
       </c>
       <c r="K67">
-        <v>1524.5760117723826</v>
+        <v>185.62751182850747</v>
       </c>
       <c r="L67">
-        <v>0.69800922775720053</v>
+        <v>1</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -5992,37 +5992,37 @@
         <v>198</v>
       </c>
       <c r="C68">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D68">
-        <v>95.649274128872605</v>
+        <v>94.417653077749918</v>
       </c>
       <c r="E68">
-        <v>86.847831158898543</v>
+        <v>86.82995976033817</v>
       </c>
       <c r="F68">
-        <v>210.20052073342586</v>
+        <v>210.29618322394634</v>
       </c>
       <c r="G68">
-        <v>5988867.0406597117</v>
+        <v>1237956.1597052447</v>
       </c>
       <c r="H68">
-        <v>7060.5850300368766</v>
+        <v>7008.7362938951992</v>
       </c>
       <c r="I68">
-        <v>47344.829598182361</v>
+        <v>46992.004705901381</v>
       </c>
       <c r="J68">
-        <v>54405.414628219238</v>
+        <v>54000.740999796581</v>
       </c>
       <c r="K68">
-        <v>2509142.4815654028</v>
+        <v>100485.20543769447</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>2.0167350801657546</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -6036,34 +6036,34 @@
         <v>198</v>
       </c>
       <c r="C69">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D69">
-        <v>95.637456687886072</v>
+        <v>93.749791652490856</v>
       </c>
       <c r="E69">
-        <v>86.846806121552859</v>
+        <v>86.895964114022419</v>
       </c>
       <c r="F69">
-        <v>210.20055149368935</v>
+        <v>210.3729293561282</v>
       </c>
       <c r="G69">
-        <v>5720213.7772797579</v>
+        <v>826488.43558793538</v>
       </c>
       <c r="H69">
-        <v>7060.1567238734087</v>
+        <v>7015.1516361937747</v>
       </c>
       <c r="I69">
-        <v>47341.919584327698</v>
+        <v>46881.049078708609</v>
       </c>
       <c r="J69">
-        <v>54402.076308201104</v>
+        <v>53896.200714902385</v>
       </c>
       <c r="K69">
-        <v>2202722.8494077842</v>
+        <v>39101.899391875806</v>
       </c>
       <c r="L69">
-        <v>2.8284628774066096</v>
+        <v>1.0649242429155452</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -6080,34 +6080,34 @@
         <v>198</v>
       </c>
       <c r="C70">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D70">
-        <v>95.663281792371677</v>
+        <v>92.997525389526601</v>
       </c>
       <c r="E70">
-        <v>86.854364618613033</v>
+        <v>87.11099692861373</v>
       </c>
       <c r="F70">
-        <v>210.201172436783</v>
+        <v>210.50064400156086</v>
       </c>
       <c r="G70">
-        <v>5045672.1014494402</v>
+        <v>529118.5383495877</v>
       </c>
       <c r="H70">
-        <v>7057.8846471557617</v>
+        <v>7056.9558352934855</v>
       </c>
       <c r="I70">
-        <v>47334.129417208271</v>
+        <v>46779.560207716953</v>
       </c>
       <c r="J70">
-        <v>54392.014064364033</v>
+        <v>53836.516043010437</v>
       </c>
       <c r="K70">
-        <v>1872103.0498055085</v>
+        <v>25618.030931210094</v>
       </c>
       <c r="L70">
-        <v>2.5705878678851777</v>
+        <v>0.68519864288061383</v>
       </c>
       <c r="M70">
         <v>0</v>
@@ -6124,34 +6124,34 @@
         <v>198</v>
       </c>
       <c r="C71">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D71">
-        <v>95.748381007272812</v>
+        <v>92.225069486420608</v>
       </c>
       <c r="E71">
-        <v>86.875456254930384</v>
+        <v>87.500333617173254</v>
       </c>
       <c r="F71">
-        <v>210.20319474759407</v>
+        <v>210.68116205189065</v>
       </c>
       <c r="G71">
-        <v>3725528.3121785834</v>
+        <v>320060.20639936515</v>
       </c>
       <c r="H71">
-        <v>7049.9570020507535</v>
+        <v>7107.726188935615</v>
       </c>
       <c r="I71">
-        <v>47310.804284158832</v>
+        <v>46656.819884717603</v>
       </c>
       <c r="J71">
-        <v>54360.761286209585</v>
+        <v>53764.546073653219</v>
       </c>
       <c r="K71">
-        <v>617314.03292359191</v>
+        <v>6747.3047899069043</v>
       </c>
       <c r="L71">
-        <v>1.8092540978164848</v>
+        <v>0.32346754597803179</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -6168,34 +6168,34 @@
         <v>198</v>
       </c>
       <c r="C72">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D72">
-        <v>95.620600321556282</v>
+        <v>91.408579251399644</v>
       </c>
       <c r="E72">
-        <v>86.872492937929565</v>
+        <v>88.02593042286972</v>
       </c>
       <c r="F72">
-        <v>210.20990669655868</v>
+        <v>210.9113325235773</v>
       </c>
       <c r="G72">
-        <v>3212754.6928247735</v>
+        <v>186313.04456050618</v>
       </c>
       <c r="H72">
-        <v>7038.1827405542026</v>
+        <v>7173.9730509428819</v>
       </c>
       <c r="I72">
-        <v>47263.74691525002</v>
+        <v>46505.778311298527</v>
       </c>
       <c r="J72">
-        <v>54301.929655804226</v>
+        <v>53679.751362241412</v>
       </c>
       <c r="K72">
-        <v>230433.00035647341</v>
+        <v>7272.1647474233769</v>
       </c>
       <c r="L72">
-        <v>1.4955813212895521</v>
+        <v>0.21587413808419403</v>
       </c>
       <c r="M72">
         <v>0</v>
@@ -6212,34 +6212,34 @@
         <v>198</v>
       </c>
       <c r="C73">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D73">
-        <v>95.220414835371201</v>
+        <v>90.36289165351819</v>
       </c>
       <c r="E73">
-        <v>86.850700234158666</v>
+        <v>88.638155422662109</v>
       </c>
       <c r="F73">
-        <v>210.23556103161582</v>
+        <v>211.20190106248893</v>
       </c>
       <c r="G73">
-        <v>2317980.3279813058</v>
+        <v>107494.3236406161</v>
       </c>
       <c r="H73">
-        <v>7029.6703527986947</v>
+        <v>7295.7830788985466</v>
       </c>
       <c r="I73">
-        <v>47165.466752180357</v>
+        <v>46304.900781992925</v>
       </c>
       <c r="J73">
-        <v>54195.137104979054</v>
+        <v>53600.68386089147</v>
       </c>
       <c r="K73">
-        <v>263162.59244457883</v>
+        <v>4370.9591049754272</v>
       </c>
       <c r="L73">
-        <v>1.2252809472632449</v>
+        <v>0.11928019645766449</v>
       </c>
       <c r="M73">
         <v>0</v>
@@ -6256,40 +6256,40 @@
         <v>198</v>
       </c>
       <c r="C74">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D74">
-        <v>94.417653077749918</v>
+        <v>88.730067738798496</v>
       </c>
       <c r="E74">
-        <v>86.82995976033817</v>
+        <v>89.448186257177866</v>
       </c>
       <c r="F74">
-        <v>210.29618322394634</v>
+        <v>211.62850313555876</v>
       </c>
       <c r="G74">
-        <v>1237956.1597052447</v>
+        <v>65860.870928385557</v>
       </c>
       <c r="H74">
-        <v>7008.7362938951992</v>
+        <v>7591.6344862006999</v>
       </c>
       <c r="I74">
-        <v>46992.004705901381</v>
+        <v>46089.857312935637</v>
       </c>
       <c r="J74">
-        <v>54000.740999796581</v>
+        <v>53681.49179913634</v>
       </c>
       <c r="K74">
-        <v>80628.341710832014</v>
+        <v>1417.1236611721922</v>
       </c>
       <c r="L74">
-        <v>0.72911339627676519</v>
+        <v>5.9230806177035092E-2</v>
       </c>
       <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
         <v>1</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -6300,34 +6300,34 @@
         <v>198</v>
       </c>
       <c r="C75">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D75">
-        <v>93.254664623692307</v>
+        <v>86.148894842236373</v>
       </c>
       <c r="E75">
-        <v>87.016139452907552</v>
+        <v>91.017385227180455</v>
       </c>
       <c r="F75">
-        <v>210.4502087416453</v>
+        <v>212.43418570642822</v>
       </c>
       <c r="G75">
-        <v>618778.46753337968</v>
+        <v>42762.939780033099</v>
       </c>
       <c r="H75">
-        <v>7049.595995478272</v>
+        <v>8305.8716463163419</v>
       </c>
       <c r="I75">
-        <v>46811.180447773433</v>
+        <v>45994.83466821038</v>
       </c>
       <c r="J75">
-        <v>53860.776443251707</v>
+        <v>54300.706314526724</v>
       </c>
       <c r="K75">
-        <v>34001.54163635656</v>
+        <v>1196.0279877877988</v>
       </c>
       <c r="L75">
-        <v>0.43235411260201934</v>
+        <v>6.4060645334863553E-2</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -6344,34 +6344,34 @@
         <v>198</v>
       </c>
       <c r="C76">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D76">
-        <v>91.913277810081354</v>
+        <v>82.658718152148012</v>
       </c>
       <c r="E76">
-        <v>87.660058381174437</v>
+        <v>94.356355141788171</v>
       </c>
       <c r="F76">
-        <v>210.75325602943414</v>
+        <v>214.02204632714711</v>
       </c>
       <c r="G76">
-        <v>266682.38535342074</v>
+        <v>29813.905104919788</v>
       </c>
       <c r="H76">
-        <v>7125.5038672930368</v>
+        <v>10047.876401517</v>
       </c>
       <c r="I76">
-        <v>46611.552882507196</v>
+        <v>46288.277623664937</v>
       </c>
       <c r="J76">
-        <v>53737.056749800235</v>
+        <v>56336.154025181939</v>
       </c>
       <c r="K76">
-        <v>10017.492506971013</v>
+        <v>620.15078370000674</v>
       </c>
       <c r="L76">
-        <v>0.20977377916665227</v>
+        <v>0.132892757458828</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -6388,40 +6388,40 @@
         <v>198</v>
       </c>
       <c r="C77">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D77">
-        <v>90.36289165351819</v>
+        <v>78.911670516030995</v>
       </c>
       <c r="E77">
-        <v>88.638155422662109</v>
+        <v>102.12067855481754</v>
       </c>
       <c r="F77">
-        <v>211.20190106248893</v>
+        <v>217.02084044184173</v>
       </c>
       <c r="G77">
-        <v>107494.3236406161</v>
+        <v>20238.068481383973</v>
       </c>
       <c r="H77">
-        <v>7295.7830788985466</v>
+        <v>14569.255730020795</v>
       </c>
       <c r="I77">
-        <v>46304.900781992925</v>
+        <v>47456.854527177857</v>
       </c>
       <c r="J77">
-        <v>53600.68386089147</v>
+        <v>62026.110257198656</v>
       </c>
       <c r="K77">
-        <v>3022.6766933995696</v>
+        <v>300.00298719318351</v>
       </c>
       <c r="L77">
-        <v>1.0720586653642847E-2</v>
+        <v>0.35990179627559526</v>
       </c>
       <c r="M77">
         <v>0</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -6432,34 +6432,34 @@
         <v>198</v>
       </c>
       <c r="C78">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D78">
-        <v>87.092740236700806</v>
+        <v>76.151282080799831</v>
       </c>
       <c r="E78">
-        <v>90.352381544771802</v>
+        <v>114.96170555873424</v>
       </c>
       <c r="F78">
-        <v>212.10100713249827</v>
+        <v>222.41782165847161</v>
       </c>
       <c r="G78">
-        <v>49149.536375396616</v>
+        <v>13982.756743889127</v>
       </c>
       <c r="H78">
-        <v>7996.8806627771764</v>
+        <v>27855.696870138887</v>
       </c>
       <c r="I78">
-        <v>45999.438494723312</v>
+        <v>49650.288605247391</v>
       </c>
       <c r="J78">
-        <v>53996.319157500489</v>
+        <v>77505.985475386275</v>
       </c>
       <c r="K78">
-        <v>770.74899847660515</v>
+        <v>64.917333336095382</v>
       </c>
       <c r="L78">
-        <v>0.49163684634898136</v>
+        <v>1</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -6476,37 +6476,37 @@
         <v>198</v>
       </c>
       <c r="C79">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D79">
-        <v>90.040862907770247</v>
+        <v>90.038839496273013</v>
       </c>
       <c r="E79">
-        <v>107.21282845389993</v>
+        <v>107.27318768125413</v>
       </c>
       <c r="F79">
-        <v>218.56853694015842</v>
+        <v>218.64403417817624</v>
       </c>
       <c r="G79">
-        <v>13993485.123185029</v>
+        <v>784059.06636060844</v>
       </c>
       <c r="H79">
-        <v>12851.324706266916</v>
+        <v>12828.362265001588</v>
       </c>
       <c r="I79">
-        <v>49184.262379670428</v>
+        <v>49149.629460118689</v>
       </c>
       <c r="J79">
-        <v>62035.587085937346</v>
+        <v>61977.991725120279</v>
       </c>
       <c r="K79">
-        <v>3862060.7776982905</v>
+        <v>89880.947393947048</v>
       </c>
       <c r="L79">
-        <v>2.9759565260357199</v>
+        <v>2.0470049601417015</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -6520,37 +6520,37 @@
         <v>198</v>
       </c>
       <c r="C80">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D80">
-        <v>90.046979297696183</v>
+        <v>90.01508294812696</v>
       </c>
       <c r="E80">
-        <v>107.21228033837279</v>
+        <v>107.298691576884</v>
       </c>
       <c r="F80">
-        <v>218.56875749719327</v>
+        <v>218.66750577294923</v>
       </c>
       <c r="G80">
-        <v>12702708.557182437</v>
+        <v>447503.23075658589</v>
       </c>
       <c r="H80">
-        <v>12850.474173499699</v>
+        <v>12809.116019671412</v>
       </c>
       <c r="I80">
-        <v>49180.673377741252</v>
+        <v>49077.001957720415</v>
       </c>
       <c r="J80">
-        <v>62031.147551240952</v>
+        <v>61886.117977391827</v>
       </c>
       <c r="K80">
-        <v>2624014.1218786933</v>
+        <v>47567.890224523559</v>
       </c>
       <c r="L80">
-        <v>2.5597590176005647</v>
+        <v>1.1365665315285529</v>
       </c>
       <c r="M80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -6564,34 +6564,34 @@
         <v>198</v>
       </c>
       <c r="C81">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D81">
-        <v>90.073406166731004</v>
+        <v>89.908183349616493</v>
       </c>
       <c r="E81">
-        <v>107.21433526420644</v>
+        <v>107.34139886202529</v>
       </c>
       <c r="F81">
-        <v>218.56922758959684</v>
+        <v>218.69381822446437</v>
       </c>
       <c r="G81">
-        <v>10308570.369092558</v>
+        <v>263641.01563208905</v>
       </c>
       <c r="H81">
-        <v>12855.807357815958</v>
+        <v>12765.06289775818</v>
       </c>
       <c r="I81">
-        <v>49185.924402388577</v>
+        <v>48961.966813139981</v>
       </c>
       <c r="J81">
-        <v>62041.731760204537</v>
+        <v>61727.029710898161</v>
       </c>
       <c r="K81">
-        <v>1851045.9406739858</v>
+        <v>18742.042865893454</v>
       </c>
       <c r="L81">
-        <v>2.1948856710644296</v>
+        <v>0.5722619342523122</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -6608,34 +6608,34 @@
         <v>198</v>
       </c>
       <c r="C82">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D82">
-        <v>90.10868518612638</v>
+        <v>89.504886248278751</v>
       </c>
       <c r="E82">
-        <v>107.21615315915508</v>
+        <v>107.44572694278098</v>
       </c>
       <c r="F82">
-        <v>218.57091173619048</v>
+        <v>218.73144526043686</v>
       </c>
       <c r="G82">
-        <v>6931509.8649934158</v>
+        <v>162953.63823911367</v>
       </c>
       <c r="H82">
-        <v>12865.508354817381</v>
+        <v>12689.985808061092</v>
       </c>
       <c r="I82">
-        <v>49197.344975219101</v>
+        <v>48768.686338921238</v>
       </c>
       <c r="J82">
-        <v>62062.85333003648</v>
+        <v>61458.672146982331</v>
       </c>
       <c r="K82">
-        <v>1435889.2555901308</v>
+        <v>12654.96167699105</v>
       </c>
       <c r="L82">
-        <v>1.8592129482865414</v>
+        <v>0.3660114676994648</v>
       </c>
       <c r="M82">
         <v>0</v>
@@ -6652,34 +6652,34 @@
         <v>198</v>
       </c>
       <c r="C83">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D83">
-        <v>90.106834503042194</v>
+        <v>88.710505819192832</v>
       </c>
       <c r="E83">
-        <v>107.22457551395212</v>
+        <v>107.68254944086164</v>
       </c>
       <c r="F83">
-        <v>218.58202486924199</v>
+        <v>218.7952526035549</v>
       </c>
       <c r="G83">
-        <v>4240702.7477938114</v>
+        <v>111982.50638973355</v>
       </c>
       <c r="H83">
-        <v>12860.378901634065</v>
+        <v>12476.21152530952</v>
       </c>
       <c r="I83">
-        <v>49211.524019289027</v>
+        <v>48531.847343372523</v>
       </c>
       <c r="J83">
-        <v>62071.902920923094</v>
+        <v>61008.058868682041</v>
       </c>
       <c r="K83">
-        <v>710076.46496966237</v>
+        <v>7143.2868793119887</v>
       </c>
       <c r="L83">
-        <v>1.4842704624424479</v>
+        <v>0.22512546936895256</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -6696,34 +6696,34 @@
         <v>198</v>
       </c>
       <c r="C84">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D84">
-        <v>90.063640941992688</v>
+        <v>86.998105131328273</v>
       </c>
       <c r="E84">
-        <v>107.24499166265898</v>
+        <v>108.25047023008419</v>
       </c>
       <c r="F84">
-        <v>218.60892281331044</v>
+        <v>218.95266435158109</v>
       </c>
       <c r="G84">
-        <v>1954447.8686692212</v>
+        <v>79347.708423338598</v>
       </c>
       <c r="H84">
-        <v>12852.23584087971</v>
+        <v>12270.956604665931</v>
       </c>
       <c r="I84">
-        <v>49216.068913245152</v>
+        <v>48290.522529756934</v>
       </c>
       <c r="J84">
-        <v>62068.30475412486</v>
+        <v>60561.479134422865</v>
       </c>
       <c r="K84">
-        <v>328702.76640362747</v>
+        <v>4053.1676507600764</v>
       </c>
       <c r="L84">
-        <v>1.2191855314709532</v>
+        <v>0.13510980376062062</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -6740,34 +6740,34 @@
         <v>198</v>
       </c>
       <c r="C85">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D85">
-        <v>90.038839496273013</v>
+        <v>84.267265269858001</v>
       </c>
       <c r="E85">
-        <v>107.27318768125413</v>
+        <v>109.49772557565355</v>
       </c>
       <c r="F85">
-        <v>218.64403417817624</v>
+        <v>219.35255458057543</v>
       </c>
       <c r="G85">
-        <v>784059.06636060844</v>
+        <v>56432.630906993181</v>
       </c>
       <c r="H85">
-        <v>12828.362265001588</v>
+        <v>12276.882899090326</v>
       </c>
       <c r="I85">
-        <v>49149.629460118689</v>
+        <v>48122.215269727494</v>
       </c>
       <c r="J85">
-        <v>61977.991725120279</v>
+        <v>60399.098168817822</v>
       </c>
       <c r="K85">
-        <v>112003.27513763303</v>
+        <v>1749.3033853889965</v>
       </c>
       <c r="L85">
-        <v>1.0193479272304993</v>
+        <v>7.4909417929908614E-2</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -6784,40 +6784,40 @@
         <v>198</v>
       </c>
       <c r="C86">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D86">
-        <v>89.939841005245555</v>
+        <v>80.328410262541937</v>
       </c>
       <c r="E86">
-        <v>107.32288638623788</v>
+        <v>112.04642771020448</v>
       </c>
       <c r="F86">
-        <v>218.68485239316561</v>
+        <v>220.26992211957136</v>
       </c>
       <c r="G86">
-        <v>308142.22968337691</v>
+        <v>40394.727884571206</v>
       </c>
       <c r="H86">
-        <v>12778.612739376409</v>
+        <v>12924.462225428477</v>
       </c>
       <c r="I86">
-        <v>49007.194344348442</v>
+        <v>48207.873359738405</v>
       </c>
       <c r="J86">
-        <v>61785.807083724852</v>
+        <v>61132.335585166882</v>
       </c>
       <c r="K86">
-        <v>40588.189443935567</v>
+        <v>1088.3207566690742</v>
       </c>
       <c r="L86">
-        <v>0.83948920874762312</v>
+        <v>6.8600454885854756E-2</v>
       </c>
       <c r="M86">
         <v>0</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -6828,34 +6828,34 @@
         <v>198</v>
       </c>
       <c r="C87">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D87">
-        <v>89.293597093562553</v>
+        <v>75.445270541854967</v>
       </c>
       <c r="E87">
-        <v>107.5015779999937</v>
+        <v>117.36063151304369</v>
       </c>
       <c r="F87">
-        <v>218.74802580954341</v>
+        <v>222.18773078518544</v>
       </c>
       <c r="G87">
-        <v>144410.87939889668</v>
+        <v>27486.771502688447</v>
       </c>
       <c r="H87">
-        <v>12626.587526142113</v>
+        <v>15128.512993012242</v>
       </c>
       <c r="I87">
-        <v>48697.013017851561</v>
+        <v>49087.620684729693</v>
       </c>
       <c r="J87">
-        <v>61323.600543993671</v>
+        <v>64216.133677741935</v>
       </c>
       <c r="K87">
-        <v>13871.283170680268</v>
+        <v>600.92041349083286</v>
       </c>
       <c r="L87">
-        <v>0.51481868547742393</v>
+        <v>0.13825829291989319</v>
       </c>
       <c r="M87">
         <v>0</v>
@@ -6872,40 +6872,40 @@
         <v>198</v>
       </c>
       <c r="C88">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D88">
-        <v>86.998105131328273</v>
+        <v>70.115779454420107</v>
       </c>
       <c r="E88">
-        <v>108.25047023008419</v>
+        <v>127.28070647184559</v>
       </c>
       <c r="F88">
-        <v>218.95266435158109</v>
+        <v>225.7664333195892</v>
       </c>
       <c r="G88">
-        <v>79347.708423338598</v>
+        <v>17454.333000279905</v>
       </c>
       <c r="H88">
-        <v>12270.956604665931</v>
+        <v>21347.797003046384</v>
       </c>
       <c r="I88">
-        <v>48290.522529756934</v>
+        <v>51104.144540234076</v>
       </c>
       <c r="J88">
-        <v>60561.479134422865</v>
+        <v>72451.941543280467</v>
       </c>
       <c r="K88">
-        <v>5785.1256218543504</v>
+        <v>387.89810972056347</v>
       </c>
       <c r="L88">
-        <v>3.4848633523200589E-3</v>
+        <v>0.3680791465961154</v>
       </c>
       <c r="M88">
         <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -6916,34 +6916,34 @@
         <v>198</v>
       </c>
       <c r="C89">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D89">
-        <v>81.842297545993347</v>
+        <v>65.729257747937169</v>
       </c>
       <c r="E89">
-        <v>110.97291106411224</v>
+        <v>141.6369868265902</v>
       </c>
       <c r="F89">
-        <v>219.87348144197247</v>
+        <v>232.21811463113426</v>
       </c>
       <c r="G89">
-        <v>44975.152142268016</v>
+        <v>11740.185076488704</v>
       </c>
       <c r="H89">
-        <v>12594.181719306527</v>
+        <v>39338.198233944167</v>
       </c>
       <c r="I89">
-        <v>48133.974640972971</v>
+        <v>54650.834944768583</v>
       </c>
       <c r="J89">
-        <v>60728.156360279499</v>
+        <v>93989.033178712751</v>
       </c>
       <c r="K89">
-        <v>1845.3217416994562</v>
+        <v>221.36499056912263</v>
       </c>
       <c r="L89">
-        <v>0.1103512983219356</v>
+        <v>1</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -6960,34 +6960,34 @@
         <v>198</v>
       </c>
       <c r="C90">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D90">
-        <v>79.24064312040565</v>
+        <v>78.249051575961346</v>
       </c>
       <c r="E90">
-        <v>127.23981343720133</v>
+        <v>127.41263750937229</v>
       </c>
       <c r="F90">
-        <v>228.07254842562935</v>
+        <v>228.21990556329749</v>
       </c>
       <c r="G90">
-        <v>15257063.850858063</v>
+        <v>4070825.3984896918</v>
       </c>
       <c r="H90">
-        <v>21190.401398299808</v>
+        <v>21058.902012138817</v>
       </c>
       <c r="I90">
-        <v>49618.969691382277</v>
+        <v>49478.327815241086</v>
       </c>
       <c r="J90">
-        <v>70809.371089682085</v>
+        <v>70537.229827379895</v>
       </c>
       <c r="K90">
-        <v>494197.40555548546</v>
+        <v>99292.562949244428</v>
       </c>
       <c r="L90">
-        <v>2.8790147642462687</v>
+        <v>2.0088317693519704</v>
       </c>
       <c r="M90">
         <v>1</v>
@@ -7004,34 +7004,34 @@
         <v>198</v>
       </c>
       <c r="C91">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D91">
-        <v>79.243239734540495</v>
+        <v>77.63895367375477</v>
       </c>
       <c r="E91">
-        <v>127.23998199299672</v>
+        <v>127.65861526096</v>
       </c>
       <c r="F91">
-        <v>228.07254851653929</v>
+        <v>228.36290093540089</v>
       </c>
       <c r="G91">
-        <v>15254823.549836893</v>
+        <v>2534356.1452514855</v>
       </c>
       <c r="H91">
-        <v>21190.448136883773</v>
+        <v>21176.725035858115</v>
       </c>
       <c r="I91">
-        <v>49619.563560110204</v>
+        <v>49405.675005253412</v>
       </c>
       <c r="J91">
-        <v>70810.011696993985</v>
+        <v>70582.400041111527</v>
       </c>
       <c r="K91">
-        <v>277626.47965322365</v>
+        <v>31032.89828264093</v>
       </c>
       <c r="L91">
-        <v>2.4911715516012367</v>
+        <v>0.94509814357063027</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -7048,34 +7048,34 @@
         <v>198</v>
       </c>
       <c r="C92">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D92">
-        <v>79.251428442258245</v>
+        <v>77.026608494953237</v>
       </c>
       <c r="E92">
-        <v>127.24051511715467</v>
+        <v>128.02860104063001</v>
       </c>
       <c r="F92">
-        <v>228.07254942139579</v>
+        <v>228.55914543100647</v>
       </c>
       <c r="G92">
-        <v>15244180.327812122</v>
+        <v>1512208.8971183486</v>
       </c>
       <c r="H92">
-        <v>21190.593500446346</v>
+        <v>21282.081185711624</v>
       </c>
       <c r="I92">
-        <v>49621.451165285762</v>
+        <v>49330.05770289855</v>
       </c>
       <c r="J92">
-        <v>70812.044665732101</v>
+        <v>70612.138888610178</v>
       </c>
       <c r="K92">
-        <v>557046.47012457799</v>
+        <v>24508.474890866986</v>
       </c>
       <c r="L92">
-        <v>2.9991501026019431</v>
+        <v>0.62948128418452143</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -7092,34 +7092,34 @@
         <v>198</v>
       </c>
       <c r="C93">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D93">
-        <v>79.277101099268009</v>
+        <v>76.41049370311751</v>
       </c>
       <c r="E93">
-        <v>127.24220193954821</v>
+        <v>128.57229289478411</v>
       </c>
       <c r="F93">
-        <v>228.0725583376385</v>
+        <v>228.8369479985362</v>
       </c>
       <c r="G93">
-        <v>14409220.659290401</v>
+        <v>831971.37956128095</v>
       </c>
       <c r="H93">
-        <v>21183.485839716028</v>
+        <v>21372.787577562285</v>
       </c>
       <c r="I93">
-        <v>49625.474975541052</v>
+        <v>49235.376969574732</v>
       </c>
       <c r="J93">
-        <v>70808.960815257073</v>
+        <v>70608.164547137014</v>
       </c>
       <c r="K93">
-        <v>530061.47834782989</v>
+        <v>17081.857269568856</v>
       </c>
       <c r="L93">
-        <v>2.8863850243902509</v>
+        <v>0.38622486177382953</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -7136,34 +7136,34 @@
         <v>198</v>
       </c>
       <c r="C94">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D94">
-        <v>79.308092806502913</v>
+        <v>75.644247922074555</v>
       </c>
       <c r="E94">
-        <v>127.2464088873531</v>
+        <v>129.18259247868895</v>
       </c>
       <c r="F94">
-        <v>228.07479547426192</v>
+        <v>229.17400785842571</v>
       </c>
       <c r="G94">
-        <v>11318792.785198895</v>
+        <v>433491.52194603771</v>
       </c>
       <c r="H94">
-        <v>21167.637816559945</v>
+        <v>21463.814552058728</v>
       </c>
       <c r="I94">
-        <v>49606.442212759735</v>
+        <v>49089.978448163711</v>
       </c>
       <c r="J94">
-        <v>70774.080029319681</v>
+        <v>70553.793000222446</v>
       </c>
       <c r="K94">
-        <v>70172.511903858773</v>
+        <v>2773.9615095362615</v>
       </c>
       <c r="L94">
-        <v>1.7518228791774768</v>
+        <v>0.13870314367476294</v>
       </c>
       <c r="M94">
         <v>0</v>
@@ -7180,34 +7180,34 @@
         <v>198</v>
       </c>
       <c r="C95">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D95">
-        <v>78.982548559809857</v>
+        <v>74.341216279785812</v>
       </c>
       <c r="E95">
-        <v>127.2608271453141</v>
+        <v>129.80673674163373</v>
       </c>
       <c r="F95">
-        <v>228.10422757126429</v>
+        <v>229.58628325309814</v>
       </c>
       <c r="G95">
-        <v>7718645.3794071395</v>
+        <v>234877.07020140468</v>
       </c>
       <c r="H95">
-        <v>21128.178524079791</v>
+        <v>21579.990703725485</v>
       </c>
       <c r="I95">
-        <v>49559.590788303707</v>
+        <v>48894.679874292939</v>
       </c>
       <c r="J95">
-        <v>70687.769312383491</v>
+        <v>70474.670578018427</v>
       </c>
       <c r="K95">
-        <v>166425.72109142496</v>
+        <v>3705.7790665080906</v>
       </c>
       <c r="L95">
-        <v>1.4316502773760917</v>
+        <v>9.2003896628227846E-2</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -7224,34 +7224,34 @@
         <v>198</v>
       </c>
       <c r="C96">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D96">
-        <v>78.249051575961346</v>
+        <v>72.072756918901277</v>
       </c>
       <c r="E96">
-        <v>127.41263750937229</v>
+        <v>130.69219537590868</v>
       </c>
       <c r="F96">
-        <v>228.21990556329749</v>
+        <v>230.21372469978044</v>
       </c>
       <c r="G96">
-        <v>4070825.3984896918</v>
+        <v>135342.83922411731</v>
       </c>
       <c r="H96">
-        <v>21058.902012138817</v>
+        <v>21720.180764233577</v>
       </c>
       <c r="I96">
-        <v>49478.327815241086</v>
+        <v>48717.718479707044</v>
       </c>
       <c r="J96">
-        <v>70537.229827379895</v>
+        <v>70437.899243940628</v>
       </c>
       <c r="K96">
-        <v>60699.401209623225</v>
+        <v>1571.8821641569502</v>
       </c>
       <c r="L96">
-        <v>0.55460889301327876</v>
+        <v>4.2633644991633822E-2</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -7268,40 +7268,40 @@
         <v>198</v>
       </c>
       <c r="C97">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D97">
-        <v>77.247342167807162</v>
+        <v>68.61089578721068</v>
       </c>
       <c r="E97">
-        <v>127.87807594169487</v>
+        <v>132.6261751366273</v>
       </c>
       <c r="F97">
-        <v>228.48052897670402</v>
+        <v>231.39072843965673</v>
       </c>
       <c r="G97">
-        <v>1807868.7598519183</v>
+        <v>84471.05600454667</v>
       </c>
       <c r="H97">
-        <v>21248.117965987269</v>
+        <v>21862.081795253373</v>
       </c>
       <c r="I97">
-        <v>49354.891474383265</v>
+        <v>48735.94865056307</v>
       </c>
       <c r="J97">
-        <v>70603.00944037053</v>
+        <v>70598.030445816446</v>
       </c>
       <c r="K97">
-        <v>21816.75567761033</v>
+        <v>544.54106140634269</v>
       </c>
       <c r="L97">
-        <v>0.53035511610558195</v>
+        <v>3.3947450730881359E-2</v>
       </c>
       <c r="M97">
         <v>0</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -7312,34 +7312,34 @@
         <v>198</v>
       </c>
       <c r="C98">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D98">
-        <v>76.223080853323495</v>
+        <v>64.314726391470884</v>
       </c>
       <c r="E98">
-        <v>128.77987488958564</v>
+        <v>137.00244708578381</v>
       </c>
       <c r="F98">
-        <v>228.94442248483267</v>
+        <v>233.49409420437433</v>
       </c>
       <c r="G98">
-        <v>667747.59524715296</v>
+        <v>54086.549517109255</v>
       </c>
       <c r="H98">
-        <v>21395.634040724355</v>
+        <v>21993.607947491644</v>
       </c>
       <c r="I98">
-        <v>49192.649444051181</v>
+        <v>49495.36902765296</v>
       </c>
       <c r="J98">
-        <v>70588.283484775544</v>
+        <v>71488.9769751446</v>
       </c>
       <c r="K98">
-        <v>7475.0561405269518</v>
+        <v>339.80569390683735</v>
       </c>
       <c r="L98">
-        <v>0.38569550960787058</v>
+        <v>0.10359462228021706</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -7356,40 +7356,40 @@
         <v>198</v>
       </c>
       <c r="C99">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D99">
-        <v>74.341216279785812</v>
+        <v>59.747668854173583</v>
       </c>
       <c r="E99">
-        <v>129.80673674163373</v>
+        <v>145.59575789485649</v>
       </c>
       <c r="F99">
-        <v>229.58628325309814</v>
+        <v>237.06435220723498</v>
       </c>
       <c r="G99">
-        <v>234877.07020140468</v>
+        <v>34368.423215274772</v>
       </c>
       <c r="H99">
-        <v>21579.990703725485</v>
+        <v>22842.715410659748</v>
       </c>
       <c r="I99">
-        <v>48894.679874292939</v>
+        <v>50906.770815552278</v>
       </c>
       <c r="J99">
-        <v>70474.670578018427</v>
+        <v>73749.48622621203</v>
       </c>
       <c r="K99">
-        <v>1158.0361372356781</v>
+        <v>111.08230706330177</v>
       </c>
       <c r="L99">
-        <v>9.0197058306278471E-3</v>
+        <v>0.29740639431028576</v>
       </c>
       <c r="M99">
         <v>0</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -7400,34 +7400,34 @@
         <v>198</v>
       </c>
       <c r="C100">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D100">
-        <v>69.961751343301714</v>
+        <v>56.283048074033786</v>
       </c>
       <c r="E100">
-        <v>131.78323955922451</v>
+        <v>157.7622178054956</v>
       </c>
       <c r="F100">
-        <v>230.90138051684852</v>
+        <v>242.97489819805969</v>
       </c>
       <c r="G100">
-        <v>98148.109503109154</v>
+        <v>22370.334897357727</v>
       </c>
       <c r="H100">
-        <v>21817.254214833603</v>
+        <v>28499.34306134213</v>
       </c>
       <c r="I100">
-        <v>48691.649119958638</v>
+        <v>53185.519218052184</v>
       </c>
       <c r="J100">
-        <v>70508.903334792238</v>
+        <v>81684.862279394321</v>
       </c>
       <c r="K100">
-        <v>1223.5465555577498</v>
+        <v>141.17600340261896</v>
       </c>
       <c r="L100">
-        <v>0.1015860936890271</v>
+        <v>1.0003034205190775</v>
       </c>
       <c r="M100">
         <v>0</v>
@@ -7444,34 +7444,34 @@
         <v>198</v>
       </c>
       <c r="C101">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="D101">
-        <v>99.887461386713497</v>
+        <v>98.911009797193159</v>
       </c>
       <c r="E101">
-        <v>67.550531046620833</v>
+        <v>67.655022822300225</v>
       </c>
       <c r="F101">
-        <v>205.05777528104886</v>
+        <v>205.10525309075177</v>
       </c>
       <c r="G101">
-        <v>6054999.4202888468</v>
+        <v>822935.59373639233</v>
       </c>
       <c r="H101">
-        <v>5253.7252184384088</v>
+        <v>5228.4112133584194</v>
       </c>
       <c r="I101">
-        <v>45528.058798903337</v>
+        <v>45285.540798509523</v>
       </c>
       <c r="J101">
-        <v>50781.78401734175</v>
+        <v>50513.952011867943</v>
       </c>
       <c r="K101">
-        <v>2381629.4384079538</v>
+        <v>47896.206879712663</v>
       </c>
       <c r="L101">
-        <v>3</v>
+        <v>2.0407777495681709</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -7488,34 +7488,34 @@
         <v>198</v>
       </c>
       <c r="C102">
-        <v>3.1622776601683792E-7</v>
+        <v>1.9952623149688788E-4</v>
       </c>
       <c r="D102">
-        <v>99.891697538401559</v>
+        <v>98.370144838865897</v>
       </c>
       <c r="E102">
-        <v>67.552627736824704</v>
+        <v>67.832129578201872</v>
       </c>
       <c r="F102">
-        <v>205.05789238565586</v>
+        <v>205.14026584467362</v>
       </c>
       <c r="G102">
-        <v>5302024.7571646105</v>
+        <v>494785.10718506289</v>
       </c>
       <c r="H102">
-        <v>5253.3218799352944</v>
+        <v>5213.764262030073</v>
       </c>
       <c r="I102">
-        <v>45526.557482137767</v>
+        <v>45201.645888115287</v>
       </c>
       <c r="J102">
-        <v>50779.879362073058</v>
+        <v>50415.410150145362</v>
       </c>
       <c r="K102">
-        <v>2025495.7294387883</v>
+        <v>28144.945088498662</v>
       </c>
       <c r="L102">
-        <v>2.7233914444105221</v>
+        <v>1.2188865770218544</v>
       </c>
       <c r="M102">
         <v>0</v>
@@ -7532,34 +7532,34 @@
         <v>198</v>
       </c>
       <c r="C103">
-        <v>9.9999999999999995E-7</v>
+        <v>3.981071705534973E-4</v>
       </c>
       <c r="D103">
-        <v>99.915775059215136</v>
+        <v>97.744699564100316</v>
       </c>
       <c r="E103">
-        <v>67.559615265398818</v>
+        <v>68.194179873905355</v>
       </c>
       <c r="F103">
-        <v>205.0583621793991</v>
+        <v>205.19443503217835</v>
       </c>
       <c r="G103">
-        <v>4549828.8592741927</v>
+        <v>291431.12268112</v>
       </c>
       <c r="H103">
-        <v>5252.2203663336022</v>
+        <v>5200.7219986538848</v>
       </c>
       <c r="I103">
-        <v>45524.117450985614</v>
+        <v>45107.917760267534</v>
       </c>
       <c r="J103">
-        <v>50776.337817319218</v>
+        <v>50308.639758921418</v>
       </c>
       <c r="K103">
-        <v>1225152.8804666654</v>
+        <v>14179.178488962105</v>
       </c>
       <c r="L103">
-        <v>2.2585970436769252</v>
+        <v>0.67090603356537648</v>
       </c>
       <c r="M103">
         <v>0</v>
@@ -7576,34 +7576,34 @@
         <v>198</v>
       </c>
       <c r="C104">
-        <v>3.1622776601683792E-6</v>
+        <v>7.9432823472428131E-4</v>
       </c>
       <c r="D104">
-        <v>99.878373918912587</v>
+        <v>97.026557582697208</v>
       </c>
       <c r="E104">
-        <v>67.562202977815701</v>
+        <v>68.744662300091278</v>
       </c>
       <c r="F104">
-        <v>205.0597922863428</v>
+        <v>205.2723777706436</v>
       </c>
       <c r="G104">
-        <v>3315909.086724672</v>
+        <v>171467.62672814395</v>
       </c>
       <c r="H104">
-        <v>5251.6976793600052</v>
+        <v>5187.0918222745195</v>
       </c>
       <c r="I104">
-        <v>45511.122151012722</v>
+        <v>44994.978777715325</v>
       </c>
       <c r="J104">
-        <v>50762.819830372726</v>
+        <v>50182.070599989842</v>
       </c>
       <c r="K104">
-        <v>605459.10007116594</v>
+        <v>7512.8256474806867</v>
       </c>
       <c r="L104">
-        <v>1.7790823694394782</v>
+        <v>0.37696361386678967</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -7620,34 +7620,34 @@
         <v>198</v>
       </c>
       <c r="C105">
-        <v>9.9999999999999991E-6</v>
+        <v>1.5848931924611141E-3</v>
       </c>
       <c r="D105">
-        <v>99.814430539479375</v>
+        <v>96.17675890652275</v>
       </c>
       <c r="E105">
-        <v>67.56967436126385</v>
+        <v>69.415972587706591</v>
       </c>
       <c r="F105">
-        <v>205.06237498590463</v>
+        <v>205.37368715379395</v>
       </c>
       <c r="G105">
-        <v>2313131.549252667</v>
+        <v>102643.16229623923</v>
       </c>
       <c r="H105">
-        <v>5254.0691556890488</v>
+        <v>5164.4049200212476</v>
       </c>
       <c r="I105">
-        <v>45480.036809189281</v>
+        <v>44853.35222136198</v>
       </c>
       <c r="J105">
-        <v>50734.105964878327</v>
+        <v>50017.757141383227</v>
       </c>
       <c r="K105">
-        <v>377933.71433184505</v>
+        <v>5433.6753476691347</v>
       </c>
       <c r="L105">
-        <v>1.4864717280211648</v>
+        <v>0.23969411620659259</v>
       </c>
       <c r="M105">
         <v>0</v>
@@ -7664,34 +7664,34 @@
         <v>198</v>
       </c>
       <c r="C106">
-        <v>3.1622776601683795E-5</v>
+        <v>3.1622776601683794E-3</v>
       </c>
       <c r="D106">
-        <v>99.549291087737174</v>
+        <v>95.079980950336648</v>
       </c>
       <c r="E106">
-        <v>67.581424471556019</v>
+        <v>70.153686865575935</v>
       </c>
       <c r="F106">
-        <v>205.07395552864796</v>
+        <v>205.50135029216403</v>
       </c>
       <c r="G106">
-        <v>1617000.4025969992</v>
+        <v>63503.499347375604</v>
       </c>
       <c r="H106">
-        <v>5252.8551531607163</v>
+        <v>5159.1730261863886</v>
       </c>
       <c r="I106">
-        <v>45420.064456992593</v>
+        <v>44683.557666334062</v>
       </c>
       <c r="J106">
-        <v>50672.919610153309</v>
+        <v>49842.730692520447</v>
       </c>
       <c r="K106">
-        <v>119747.0555285227</v>
+        <v>2030.5614900572068</v>
       </c>
       <c r="L106">
-        <v>1.1973091876914035</v>
+        <v>0.11061688433556721</v>
       </c>
       <c r="M106">
         <v>0</v>
@@ -7708,34 +7708,34 @@
         <v>198</v>
       </c>
       <c r="C107">
-        <v>1E-4</v>
+        <v>6.3095734448019303E-3</v>
       </c>
       <c r="D107">
-        <v>98.911009797193159</v>
+        <v>93.53406378951496</v>
       </c>
       <c r="E107">
-        <v>67.655022822300225</v>
+        <v>71.062034723873396</v>
       </c>
       <c r="F107">
-        <v>205.10525309075177</v>
+        <v>205.68846850740539</v>
       </c>
       <c r="G107">
-        <v>822935.59373639233</v>
+        <v>41277.375167812126</v>
       </c>
       <c r="H107">
-        <v>5228.4112133584194</v>
+        <v>5258.5816891346931</v>
       </c>
       <c r="I107">
-        <v>45285.540798509523</v>
+        <v>44527.223420209477</v>
       </c>
       <c r="J107">
-        <v>50513.952011867943</v>
+        <v>49785.805109344168</v>
       </c>
       <c r="K107">
-        <v>43570.160362221803</v>
+        <v>1067.1591369933562</v>
       </c>
       <c r="L107">
-        <v>0.86420708888436748</v>
+        <v>5.9964679232040977E-2</v>
       </c>
       <c r="M107">
         <v>0</v>
@@ -7752,40 +7752,40 @@
         <v>198</v>
       </c>
       <c r="C108">
-        <v>3.1622776601683794E-4</v>
+        <v>1.2589254117941675E-2</v>
       </c>
       <c r="D108">
-        <v>98.002519737426553</v>
+        <v>91.370631260394163</v>
       </c>
       <c r="E108">
-        <v>68.054029579607842</v>
+        <v>72.746553046276532</v>
       </c>
       <c r="F108">
-        <v>205.17219939550847</v>
+        <v>206.05915655500243</v>
       </c>
       <c r="G108">
-        <v>352936.39399437665</v>
+        <v>26882.671810963799</v>
       </c>
       <c r="H108">
-        <v>5208.1107406769606</v>
+        <v>5649.3966025344889</v>
       </c>
       <c r="I108">
-        <v>45142.865085605175</v>
+        <v>44517.434963067426</v>
       </c>
       <c r="J108">
-        <v>50350.975826282134</v>
+        <v>50166.831565601911</v>
       </c>
       <c r="K108">
-        <v>15482.621186178323</v>
+        <v>337.06988775001969</v>
       </c>
       <c r="L108">
-        <v>0.60083211843143802</v>
+        <v>4.8342914355379435E-2</v>
       </c>
       <c r="M108">
         <v>0</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -7796,34 +7796,34 @@
         <v>198</v>
       </c>
       <c r="C109">
-        <v>1E-3</v>
+        <v>2.5118864315095794E-2</v>
       </c>
       <c r="D109">
-        <v>96.723642094017151</v>
+        <v>88.679411640643323</v>
       </c>
       <c r="E109">
-        <v>68.955853408316102</v>
+        <v>75.883890742110509</v>
       </c>
       <c r="F109">
-        <v>205.30516465784675</v>
+        <v>206.87264120709798</v>
       </c>
       <c r="G109">
-        <v>143926.88341310824</v>
+        <v>18651.920420878101</v>
       </c>
       <c r="H109">
-        <v>5180.7262964960819</v>
+        <v>6836.4112154792083</v>
       </c>
       <c r="I109">
-        <v>44951.397189309493</v>
+        <v>44918.228651857848</v>
       </c>
       <c r="J109">
-        <v>50132.123485805576</v>
+        <v>51754.639867337057</v>
       </c>
       <c r="K109">
-        <v>4383.7226518586067</v>
+        <v>221.53128738083669</v>
       </c>
       <c r="L109">
-        <v>0.32841660627756475</v>
+        <v>0.12473168969538455</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -7840,40 +7840,40 @@
         <v>198</v>
       </c>
       <c r="C110">
-        <v>3.1622776601683794E-3</v>
+        <v>5.0118723362727248E-2</v>
       </c>
       <c r="D110">
-        <v>95.079980950336648</v>
+        <v>85.759567163516536</v>
       </c>
       <c r="E110">
-        <v>70.153686865575935</v>
+        <v>81.77529110917267</v>
       </c>
       <c r="F110">
-        <v>205.50135029216403</v>
+        <v>208.58447904636034</v>
       </c>
       <c r="G110">
-        <v>63503.499347375604</v>
+        <v>12975.29334833436</v>
       </c>
       <c r="H110">
-        <v>5159.1730261863886</v>
+        <v>10115.219500038625</v>
       </c>
       <c r="I110">
-        <v>44683.557666334062</v>
+        <v>45990.425089963261</v>
       </c>
       <c r="J110">
-        <v>49842.730692520447</v>
+        <v>56105.644590001888</v>
       </c>
       <c r="K110">
-        <v>1344.444908279776</v>
+        <v>102.09202983977367</v>
       </c>
       <c r="L110">
-        <v>5.614015016895799E-3</v>
+        <v>0.35892262532502744</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -7884,34 +7884,34 @@
         <v>198</v>
       </c>
       <c r="C111">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D111">
-        <v>92.210831250369395</v>
+        <v>83.774898699878079</v>
       </c>
       <c r="E111">
-        <v>72.0539069194148</v>
+        <v>92.157081133255886</v>
       </c>
       <c r="F111">
-        <v>205.89886688917548</v>
+        <v>211.92664625360112</v>
       </c>
       <c r="G111">
-        <v>31240.181197983278</v>
+        <v>9250.8271674980861</v>
       </c>
       <c r="H111">
-        <v>5468.6809922284656</v>
+        <v>19610.915118597622</v>
       </c>
       <c r="I111">
-        <v>44489.817348224155</v>
+        <v>48031.365893284528</v>
       </c>
       <c r="J111">
-        <v>49958.498340452621</v>
+        <v>67642.281011882151</v>
       </c>
       <c r="K111">
-        <v>730.16230493879095</v>
+        <v>81.95689303640431</v>
       </c>
       <c r="L111">
-        <v>0.12328122894853111</v>
+        <v>1</v>
       </c>
       <c r="M111">
         <v>0</v>
